--- a/JPN_WB_timeseries.xlsx
+++ b/JPN_WB_timeseries.xlsx
@@ -14,15 +14,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -383,12 +464,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -399,355 +480,2242 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:31">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>1.22991895675659</v>
+      </c>
+      <c r="F2">
+        <v>2.63045548903539</v>
+      </c>
+      <c r="G2">
+        <v>208.815005555476</v>
+      </c>
+      <c r="H2">
+        <v>10.4634942027505</v>
+      </c>
+      <c r="I2">
         <v>2.76464755136783</v>
       </c>
-      <c r="C2">
+      <c r="J2">
+        <v>27287.2701912718</v>
+      </c>
+      <c r="K2">
+        <v>39169.3595701504</v>
+      </c>
+      <c r="L2">
+        <v>2.59289108643961</v>
+      </c>
+      <c r="N2">
+        <v>1.14183568954468</v>
+      </c>
+      <c r="O2">
+        <v>16.549191407008</v>
+      </c>
+      <c r="P2">
+        <v>17.1095576406981</v>
+      </c>
+      <c r="Q2">
+        <v>9.09887738115494</v>
+      </c>
+      <c r="R2">
         <v>-0.67657868359508</v>
       </c>
-      <c r="D2">
+      <c r="S2">
+        <v>81.0760975609756</v>
+      </c>
+      <c r="T2">
+        <v>0.915985609742523</v>
+      </c>
+      <c r="U2">
+        <v>1.19755268096924</v>
+      </c>
+      <c r="V2">
+        <v>126843000</v>
+      </c>
+      <c r="X2">
+        <v>0.797354161739349</v>
+      </c>
+      <c r="Y2">
+        <v>1.28975915908813</v>
+      </c>
+      <c r="Z2">
+        <v>361639097011.665</v>
+      </c>
+      <c r="AA2">
+        <v>8.79520531144647</v>
+      </c>
+      <c r="AB2">
+        <v>19.5623715839054</v>
+      </c>
+      <c r="AC2">
         <v>4.748</v>
       </c>
+      <c r="AD2">
+        <v>78.649</v>
+      </c>
+      <c r="AE2">
+        <v>0.958087980747223</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:31">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>1.83473615884929</v>
+      </c>
+      <c r="F3">
+        <v>1.97087092323799</v>
+      </c>
+      <c r="G3">
+        <v>180.201537127819</v>
+      </c>
+      <c r="H3">
+        <v>10.0767999632844</v>
+      </c>
+      <c r="I3">
         <v>0.386103426142029</v>
       </c>
-      <c r="C3">
+      <c r="J3">
+        <v>27942.346651133</v>
+      </c>
+      <c r="K3">
+        <v>34406.1824638092</v>
+      </c>
+      <c r="L3">
+        <v>0.144511690081188</v>
+      </c>
+      <c r="O3">
+        <v>17.2289905143177</v>
+      </c>
+      <c r="P3">
+        <v>16.2333992095233</v>
+      </c>
+      <c r="Q3">
+        <v>9.48280450872269</v>
+      </c>
+      <c r="R3">
         <v>-0.740055504162812</v>
       </c>
-      <c r="D3">
+      <c r="S3">
+        <v>81.4163414634146</v>
+      </c>
+      <c r="T3">
+        <v>0.931672842050063</v>
+      </c>
+      <c r="V3">
+        <v>127149000</v>
+      </c>
+      <c r="Z3">
+        <v>401957624245.241</v>
+      </c>
+      <c r="AA3">
+        <v>10.694240054348</v>
+      </c>
+      <c r="AB3">
+        <v>19.5596044720071</v>
+      </c>
+      <c r="AC3">
         <v>5.02</v>
       </c>
+      <c r="AD3">
+        <v>79.98999999999999</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:31">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="C4">
+        <v>2.74454290022872</v>
+      </c>
+      <c r="E4">
+        <v>0.936939835548401</v>
+      </c>
+      <c r="F4">
+        <v>2.60256520794997</v>
+      </c>
+      <c r="G4">
+        <v>177.918035565601</v>
+      </c>
+      <c r="H4">
+        <v>10.8554456072287</v>
+      </c>
+      <c r="I4">
         <v>0.0419624992862282</v>
       </c>
-      <c r="C4">
+      <c r="J4">
+        <v>28623.5884479367</v>
+      </c>
+      <c r="K4">
+        <v>32820.7936433254</v>
+      </c>
+      <c r="L4">
+        <v>-0.190392013639268</v>
+      </c>
+      <c r="N4">
+        <v>1.0168479681015</v>
+      </c>
+      <c r="O4">
+        <v>17.7749067788644</v>
+      </c>
+      <c r="P4">
+        <v>16.1070602104528</v>
+      </c>
+      <c r="Q4">
+        <v>9.5916764589296</v>
+      </c>
+      <c r="R4">
         <v>-0.923494026942286</v>
       </c>
-      <c r="D4">
+      <c r="S4">
+        <v>81.6907317073171</v>
+      </c>
+      <c r="T4">
+        <v>0.940357539781883</v>
+      </c>
+      <c r="U4">
+        <v>1.17602252960205</v>
+      </c>
+      <c r="V4">
+        <v>127445000</v>
+      </c>
+      <c r="X4">
+        <v>0.495340138673782</v>
+      </c>
+      <c r="Y4">
+        <v>1.14855170249939</v>
+      </c>
+      <c r="Z4">
+        <v>469618129427.641</v>
+      </c>
+      <c r="AA4">
+        <v>13.0738264108092</v>
+      </c>
+      <c r="AB4">
+        <v>20.4471220661583</v>
+      </c>
+      <c r="AC4">
         <v>5.386</v>
       </c>
+      <c r="AD4">
+        <v>81.64700000000001</v>
+      </c>
+      <c r="AE4">
+        <v>1.01447093486786</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:31">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>3.79788955328764</v>
+      </c>
+      <c r="E5">
+        <v>1.16987371444702</v>
+      </c>
+      <c r="F5">
+        <v>3.08393890811207</v>
+      </c>
+      <c r="G5">
+        <v>177.536325650048</v>
+      </c>
+      <c r="H5">
+        <v>11.4658015766594</v>
+      </c>
+      <c r="I5">
         <v>1.53512549946694</v>
       </c>
-      <c r="C5">
+      <c r="J5">
+        <v>29392.2489916186</v>
+      </c>
+      <c r="K5">
+        <v>35387.0374203599</v>
+      </c>
+      <c r="L5">
+        <v>1.31809196260171</v>
+      </c>
+      <c r="N5">
+        <v>1.15746104717255</v>
+      </c>
+      <c r="O5">
+        <v>17.8364695899716</v>
+      </c>
+      <c r="P5">
+        <v>15.7293776764486</v>
+      </c>
+      <c r="Q5">
+        <v>9.860323691152489</v>
+      </c>
+      <c r="R5">
         <v>-0.25654181631606</v>
       </c>
-      <c r="D5">
+      <c r="S5">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.940046609654355</v>
+      </c>
+      <c r="U5">
+        <v>1.0271201133728</v>
+      </c>
+      <c r="V5">
+        <v>127718000</v>
+      </c>
+      <c r="X5">
+        <v>1.0699657201767</v>
+      </c>
+      <c r="Y5">
+        <v>1.16399013996124</v>
+      </c>
+      <c r="Z5">
+        <v>673554461758.647</v>
+      </c>
+      <c r="AA5">
+        <v>17.0649282535659</v>
+      </c>
+      <c r="AB5">
+        <v>21.3261252678119</v>
+      </c>
+      <c r="AC5">
         <v>5.251</v>
       </c>
+      <c r="AD5">
+        <v>83.196</v>
+      </c>
+      <c r="AE5">
+        <v>1.08260369300842</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:31">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>4.22878423179129</v>
+      </c>
+      <c r="E6">
+        <v>1.20001101493835</v>
+      </c>
+      <c r="F6">
+        <v>3.71938350458584</v>
+      </c>
+      <c r="G6">
+        <v>170.771866840423</v>
+      </c>
+      <c r="H6">
+        <v>12.7862646247862</v>
+      </c>
+      <c r="I6">
         <v>2.18611569439318</v>
       </c>
-      <c r="C6">
+      <c r="J6">
+        <v>30830.6584466434</v>
+      </c>
+      <c r="K6">
+        <v>38298.9801712303</v>
+      </c>
+      <c r="L6">
+        <v>2.15172332915763</v>
+      </c>
+      <c r="N6">
+        <v>1.34332299232483</v>
+      </c>
+      <c r="O6">
+        <v>17.7233548337375</v>
+      </c>
+      <c r="P6">
+        <v>15.0737560136373</v>
+      </c>
+      <c r="Q6">
+        <v>10.8780887981112</v>
+      </c>
+      <c r="R6">
         <v>-0.008573388203060431</v>
       </c>
-      <c r="D6">
+      <c r="S6">
+        <v>82.030243902439</v>
+      </c>
+      <c r="T6">
+        <v>0.926604015973528</v>
+      </c>
+      <c r="U6">
+        <v>1.02831530570984</v>
+      </c>
+      <c r="V6">
+        <v>127761000</v>
+      </c>
+      <c r="X6">
+        <v>1.1344233751297</v>
+      </c>
+      <c r="Y6">
+        <v>1.24947249889374</v>
+      </c>
+      <c r="Z6">
+        <v>844667163385.489</v>
+      </c>
+      <c r="AA6">
+        <v>17.9567856611529</v>
+      </c>
+      <c r="AB6">
+        <v>23.6643534228975</v>
+      </c>
+      <c r="AC6">
         <v>4.734</v>
       </c>
+      <c r="AD6">
+        <v>84.64</v>
+      </c>
+      <c r="AE6">
+        <v>1.04349458217621</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:31">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="C7">
+        <v>4.38690182974916</v>
+      </c>
+      <c r="E7">
+        <v>1.2101241350174</v>
+      </c>
+      <c r="F7">
+        <v>3.52114065640567</v>
+      </c>
+      <c r="G7">
+        <v>170.710867437499</v>
+      </c>
+      <c r="H7">
+        <v>13.8158957221159</v>
+      </c>
+      <c r="I7">
         <v>1.80390087215821</v>
       </c>
-      <c r="C7">
+      <c r="J7">
+        <v>32169.867493646</v>
+      </c>
+      <c r="K7">
+        <v>37812.8950199948</v>
+      </c>
+      <c r="L7">
+        <v>1.79433980048837</v>
+      </c>
+      <c r="N7">
+        <v>1.28548622131348</v>
+      </c>
+      <c r="O7">
+        <v>17.7438933244397</v>
+      </c>
+      <c r="P7">
+        <v>15.0518407348066</v>
+      </c>
+      <c r="Q7">
+        <v>12.4140588557406</v>
+      </c>
+      <c r="R7">
         <v>-0.282946068764429</v>
       </c>
-      <c r="D7">
+      <c r="S7">
+        <v>81.9551219512195</v>
+      </c>
+      <c r="T7">
+        <v>0.916916800183882</v>
+      </c>
+      <c r="U7">
+        <v>1.03576946258545</v>
+      </c>
+      <c r="V7">
+        <v>127773000</v>
+      </c>
+      <c r="X7">
+        <v>1.25873100757599</v>
+      </c>
+      <c r="Y7">
+        <v>1.22439658641815</v>
+      </c>
+      <c r="Z7">
+        <v>846895906145.13</v>
+      </c>
+      <c r="AA7">
+        <v>15.8351701910594</v>
+      </c>
+      <c r="AB7">
+        <v>26.2299545778565</v>
+      </c>
+      <c r="AC7">
         <v>4.446</v>
       </c>
+      <c r="AD7">
+        <v>85.97799999999999</v>
+      </c>
+      <c r="AE7">
+        <v>1.0062769651413</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:31">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="C8">
+        <v>1.82143853415748</v>
+      </c>
+      <c r="E8">
+        <v>1.3208487033844</v>
+      </c>
+      <c r="F8">
+        <v>3.79586172862876</v>
+      </c>
+      <c r="G8">
+        <v>168.922428789944</v>
+      </c>
+      <c r="H8">
+        <v>15.6573740466117</v>
+      </c>
+      <c r="I8">
         <v>1.3723501275831</v>
       </c>
-      <c r="C8">
+      <c r="J8">
+        <v>33634.6317066787</v>
+      </c>
+      <c r="K8">
+        <v>35991.546002862</v>
+      </c>
+      <c r="L8">
+        <v>1.3081271829718</v>
+      </c>
+      <c r="N8">
+        <v>1.5849609375</v>
+      </c>
+      <c r="O8">
+        <v>17.595075361072</v>
+      </c>
+      <c r="P8">
+        <v>14.8453333163917</v>
+      </c>
+      <c r="Q8">
+        <v>14.3590020520575</v>
+      </c>
+      <c r="R8">
         <v>0.249355116079105</v>
       </c>
-      <c r="D8">
+      <c r="S8">
+        <v>82.3219512195122</v>
+      </c>
+      <c r="T8">
+        <v>0.902988432465036</v>
+      </c>
+      <c r="U8">
+        <v>1.13833451271057</v>
+      </c>
+      <c r="V8">
+        <v>127854000</v>
+      </c>
+      <c r="X8">
+        <v>1.26020288467407</v>
+      </c>
+      <c r="Y8">
+        <v>1.35152566432953</v>
+      </c>
+      <c r="Z8">
+        <v>895321278049.835</v>
+      </c>
+      <c r="AA8">
+        <v>15.0181261034339</v>
+      </c>
+      <c r="AB8">
+        <v>30.0163760986692</v>
+      </c>
+      <c r="AC8">
         <v>4.192</v>
       </c>
+      <c r="AD8">
+        <v>87.11799999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0.954123318195343</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:31">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="C9">
+        <v>1.8254105730288</v>
+      </c>
+      <c r="E9">
+        <v>1.23022782802582</v>
+      </c>
+      <c r="F9">
+        <v>4.62330048259255</v>
+      </c>
+      <c r="G9">
+        <v>162.66502275156</v>
+      </c>
+      <c r="H9">
+        <v>17.2891273707229</v>
+      </c>
+      <c r="I9">
         <v>1.48396941157472</v>
       </c>
-      <c r="C9">
+      <c r="J9">
+        <v>35015.9865745127</v>
+      </c>
+      <c r="K9">
+        <v>35779.0245416427</v>
+      </c>
+      <c r="L9">
+        <v>1.36742232597771</v>
+      </c>
+      <c r="N9">
+        <v>1.44125950336456</v>
+      </c>
+      <c r="O9">
+        <v>17.6343087480996</v>
+      </c>
+      <c r="P9">
+        <v>14.0037943063894</v>
+      </c>
+      <c r="Q9">
+        <v>15.5274506811561</v>
+      </c>
+      <c r="R9">
         <v>0.0600394544986545</v>
       </c>
-      <c r="D9">
+      <c r="S9">
+        <v>82.5070731707317</v>
+      </c>
+      <c r="T9">
+        <v>0.884987382290183</v>
+      </c>
+      <c r="U9">
+        <v>1.01037454605103</v>
+      </c>
+      <c r="V9">
+        <v>128001000</v>
+      </c>
+      <c r="X9">
+        <v>1.12917721271515</v>
+      </c>
+      <c r="Y9">
+        <v>1.31983089447021</v>
+      </c>
+      <c r="Z9">
+        <v>973296740492.651</v>
+      </c>
+      <c r="AA9">
+        <v>15.0050233221166</v>
+      </c>
+      <c r="AB9">
+        <v>32.816578051879</v>
+      </c>
+      <c r="AC9">
         <v>3.888</v>
       </c>
+      <c r="AD9">
+        <v>88.146</v>
+      </c>
+      <c r="AE9">
+        <v>0.969946265220642</v>
+      </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:31">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
-      <c r="B10">
+      <c r="C10">
+        <v>2.40594837260353</v>
+      </c>
+      <c r="E10">
+        <v>1.32388854026794</v>
+      </c>
+      <c r="F10">
+        <v>2.78294234789655</v>
+      </c>
+      <c r="G10">
+        <v>160.726117314149</v>
+      </c>
+      <c r="H10">
+        <v>17.2355433764071</v>
+      </c>
+      <c r="I10">
         <v>-1.22428900061713</v>
       </c>
-      <c r="C10">
+      <c r="J10">
+        <v>35273.791152156</v>
+      </c>
+      <c r="K10">
+        <v>39876.3039685725</v>
+      </c>
+      <c r="L10">
+        <v>-1.27210994875956</v>
+      </c>
+      <c r="M10">
+        <v>34.6</v>
+      </c>
+      <c r="N10">
+        <v>1.45174884796143</v>
+      </c>
+      <c r="O10">
+        <v>18.025030322619</v>
+      </c>
+      <c r="P10">
+        <v>15.2644121011595</v>
+      </c>
+      <c r="Q10">
+        <v>16.8939331648175</v>
+      </c>
+      <c r="R10">
         <v>1.38007886164926</v>
       </c>
-      <c r="D10">
+      <c r="S10">
+        <v>82.5875609756098</v>
+      </c>
+      <c r="T10">
+        <v>0.907855045566342</v>
+      </c>
+      <c r="U10">
+        <v>0.894625246524811</v>
+      </c>
+      <c r="V10">
+        <v>128063000</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1.13206923007965</v>
+      </c>
+      <c r="Y10">
+        <v>1.30866920948029</v>
+      </c>
+      <c r="Z10">
+        <v>1030762755205.19</v>
+      </c>
+      <c r="AA10">
+        <v>13.3310524110076</v>
+      </c>
+      <c r="AB10">
+        <v>34.1294765412245</v>
+      </c>
+      <c r="AC10">
         <v>4.002</v>
       </c>
+      <c r="AD10">
+        <v>89.10299999999999</v>
+      </c>
+      <c r="AE10">
+        <v>0.948859214782715</v>
+      </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:31">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
-      <c r="B11">
+      <c r="C11">
+        <v>2.86970655915394</v>
+      </c>
+      <c r="E11">
+        <v>1.36922454833984</v>
+      </c>
+      <c r="F11">
+        <v>2.75409583494435</v>
+      </c>
+      <c r="G11">
+        <v>167.768231359701</v>
+      </c>
+      <c r="H11">
+        <v>12.41956574798</v>
+      </c>
+      <c r="I11">
         <v>-5.69323635892741</v>
       </c>
-      <c r="C11">
+      <c r="J11">
+        <v>33547.2834245767</v>
+      </c>
+      <c r="K11">
+        <v>41308.9968370512</v>
+      </c>
+      <c r="L11">
+        <v>-5.68145234041657</v>
+      </c>
+      <c r="M11">
+        <v>33</v>
+      </c>
+      <c r="N11">
+        <v>1.45010435581207</v>
+      </c>
+      <c r="O11">
+        <v>19.3337393097808</v>
+      </c>
+      <c r="P11">
+        <v>18.2117006884089</v>
+      </c>
+      <c r="Q11">
+        <v>11.9706007858756</v>
+      </c>
+      <c r="R11">
         <v>-1.35283672951723</v>
       </c>
-      <c r="D11">
+      <c r="S11">
+        <v>82.93146341463419</v>
+      </c>
+      <c r="T11">
+        <v>0.972969565505525</v>
+      </c>
+      <c r="U11">
+        <v>0.976251900196075</v>
+      </c>
+      <c r="V11">
+        <v>128047000</v>
+      </c>
+      <c r="W11">
+        <v>0.9</v>
+      </c>
+      <c r="X11">
+        <v>1.09656965732574</v>
+      </c>
+      <c r="Y11">
+        <v>1.28708302974701</v>
+      </c>
+      <c r="Z11">
+        <v>1051654952502.29</v>
+      </c>
+      <c r="AA11">
+        <v>18.3847316266499</v>
+      </c>
+      <c r="AB11">
+        <v>24.3901665338555</v>
+      </c>
+      <c r="AC11">
         <v>5.068</v>
       </c>
+      <c r="AD11">
+        <v>89.989</v>
+      </c>
+      <c r="AE11">
+        <v>1.02105367183685</v>
+      </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:31">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
-      <c r="B12">
+      <c r="C12">
+        <v>3.05326200516724</v>
+      </c>
+      <c r="D12">
+        <v>2.45650253168859</v>
+      </c>
+      <c r="E12">
+        <v>1.55362319946289</v>
+      </c>
+      <c r="F12">
+        <v>3.83547896264376</v>
+      </c>
+      <c r="G12">
+        <v>159.629862168581</v>
+      </c>
+      <c r="H12">
+        <v>14.9185034496428</v>
+      </c>
+      <c r="I12">
         <v>4.09791791943181</v>
       </c>
-      <c r="C12">
+      <c r="J12">
+        <v>35335.3735103814</v>
+      </c>
+      <c r="K12">
+        <v>44968.1562349739</v>
+      </c>
+      <c r="L12">
+        <v>4.07922304856318</v>
+      </c>
+      <c r="M12">
+        <v>31.5</v>
+      </c>
+      <c r="N12">
+        <v>1.52235090732574</v>
+      </c>
+      <c r="O12">
+        <v>19.2025962424431</v>
+      </c>
+      <c r="P12">
+        <v>17.2217468141394</v>
+      </c>
+      <c r="Q12">
+        <v>13.5799692441961</v>
+      </c>
+      <c r="R12">
         <v>-0.7282432075177659</v>
       </c>
-      <c r="D12">
+      <c r="S12">
+        <v>82.8426829268293</v>
+      </c>
+      <c r="T12">
+        <v>0.94903256103587</v>
+      </c>
+      <c r="U12">
+        <v>0.879353165626526</v>
+      </c>
+      <c r="V12">
+        <v>128070000</v>
+      </c>
+      <c r="W12">
+        <v>0.7</v>
+      </c>
+      <c r="X12">
+        <v>1.0166825056076</v>
+      </c>
+      <c r="Y12">
+        <v>1.31965863704681</v>
+      </c>
+      <c r="Z12">
+        <v>1104563760972.06</v>
+      </c>
+      <c r="AA12">
+        <v>15.8070134520484</v>
+      </c>
+      <c r="AB12">
+        <v>28.4984726938389</v>
+      </c>
+      <c r="AC12">
         <v>5.102</v>
       </c>
+      <c r="AD12">
+        <v>90.812</v>
+      </c>
+      <c r="AE12">
+        <v>1.04070508480072</v>
+      </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:31">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
-      <c r="B13">
+      <c r="C13">
+        <v>4.44439654155868</v>
+      </c>
+      <c r="D13">
+        <v>2.44741326110445</v>
+      </c>
+      <c r="E13">
+        <v>1.55437541007996</v>
+      </c>
+      <c r="F13">
+        <v>2.07915328846556</v>
+      </c>
+      <c r="G13">
+        <v>158.768146838801</v>
+      </c>
+      <c r="H13">
+        <v>14.7744622613499</v>
+      </c>
+      <c r="I13">
         <v>0.0238095237995424</v>
       </c>
-      <c r="C13">
+      <c r="J13">
+        <v>36214.4397740241</v>
+      </c>
+      <c r="K13">
+        <v>48760.0789494211</v>
+      </c>
+      <c r="L13">
+        <v>0.209251802844406</v>
+      </c>
+      <c r="M13">
+        <v>33</v>
+      </c>
+      <c r="N13">
+        <v>1.46691274642944</v>
+      </c>
+      <c r="O13">
+        <v>19.885399284228</v>
+      </c>
+      <c r="P13">
+        <v>18.5956788727445</v>
+      </c>
+      <c r="Q13">
+        <v>15.4204984672798</v>
+      </c>
+      <c r="R13">
         <v>-0.272455616101245</v>
       </c>
-      <c r="D13">
+      <c r="S13">
+        <v>82.5912195121951</v>
+      </c>
+      <c r="T13">
+        <v>0.974823549750829</v>
+      </c>
+      <c r="U13">
+        <v>0.99509197473526</v>
+      </c>
+      <c r="V13">
+        <v>127833000</v>
+      </c>
+      <c r="W13">
+        <v>0.5</v>
+      </c>
+      <c r="X13">
+        <v>1.07426130771637</v>
+      </c>
+      <c r="Y13">
+        <v>1.30369925498962</v>
+      </c>
+      <c r="Z13">
+        <v>1295838676317.29</v>
+      </c>
+      <c r="AA13">
+        <v>15.2333155611711</v>
+      </c>
+      <c r="AB13">
+        <v>30.1949607286296</v>
+      </c>
+      <c r="AC13">
         <v>4.55</v>
       </c>
+      <c r="AD13">
+        <v>91.069</v>
+      </c>
+      <c r="AE13">
+        <v>1.07113337516785</v>
+      </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:31">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
-      <c r="B14">
+      <c r="C14">
+        <v>5.34915931906186</v>
+      </c>
+      <c r="D14">
+        <v>2.42889160930217</v>
+      </c>
+      <c r="E14">
+        <v>1.61894869804382</v>
+      </c>
+      <c r="F14">
+        <v>0.95844261141204</v>
+      </c>
+      <c r="G14">
+        <v>159.302098587601</v>
+      </c>
+      <c r="H14">
+        <v>14.4147746129824</v>
+      </c>
+      <c r="I14">
         <v>1.37475099905274</v>
       </c>
-      <c r="C14">
+      <c r="J14">
+        <v>37605.9742614539</v>
+      </c>
+      <c r="K14">
+        <v>49145.2804308193</v>
+      </c>
+      <c r="L14">
+        <v>1.53678665868971</v>
+      </c>
+      <c r="M14">
+        <v>32.5</v>
+      </c>
+      <c r="N14">
+        <v>1.40798962116241</v>
+      </c>
+      <c r="O14">
+        <v>19.9573325085164</v>
+      </c>
+      <c r="P14">
+        <v>18.1117047475127</v>
+      </c>
+      <c r="Q14">
+        <v>16.0561363041928</v>
+      </c>
+      <c r="R14">
         <v>-0.0440645104432608</v>
       </c>
-      <c r="D14">
+      <c r="S14">
+        <v>83.09609756097559</v>
+      </c>
+      <c r="T14">
+        <v>0.956761841659896</v>
+      </c>
+      <c r="U14">
+        <v>0.948442876338959</v>
+      </c>
+      <c r="V14">
+        <v>127629000</v>
+      </c>
+      <c r="W14">
+        <v>1.5</v>
+      </c>
+      <c r="X14">
+        <v>1.13758063316345</v>
+      </c>
+      <c r="Y14">
+        <v>1.35136580467224</v>
+      </c>
+      <c r="Z14">
+        <v>1268085524238.3</v>
+      </c>
+      <c r="AA14">
+        <v>14.2347343263613</v>
+      </c>
+      <c r="AB14">
+        <v>30.4709109171752</v>
+      </c>
+      <c r="AC14">
         <v>4.358</v>
       </c>
+      <c r="AD14">
+        <v>91.148</v>
+      </c>
+      <c r="AE14">
+        <v>1.10129523277283</v>
+      </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:31">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>4.74092949948218</v>
+      </c>
+      <c r="C15">
+        <v>10.9156317688722</v>
+      </c>
+      <c r="D15">
+        <v>2.12909018123307</v>
+      </c>
+      <c r="E15">
+        <v>1.6482492685318</v>
+      </c>
+      <c r="F15">
+        <v>0.8897854158088629</v>
+      </c>
+      <c r="G15">
+        <v>162.702815762356</v>
+      </c>
+      <c r="H15">
+        <v>15.7841567318773</v>
+      </c>
+      <c r="I15">
         <v>2.00510017681211</v>
       </c>
-      <c r="C15">
+      <c r="J15">
+        <v>39402.0250988025</v>
+      </c>
+      <c r="K15">
+        <v>40898.6478964744</v>
+      </c>
+      <c r="L15">
+        <v>2.15237106568597</v>
+      </c>
+      <c r="M15">
+        <v>31.5</v>
+      </c>
+      <c r="N15">
+        <v>1.61050939559937</v>
+      </c>
+      <c r="O15">
+        <v>19.854370134417</v>
+      </c>
+      <c r="P15">
+        <v>18.1406509054638</v>
+      </c>
+      <c r="Q15">
+        <v>18.1946119190738</v>
+      </c>
+      <c r="R15">
         <v>0.335037912184772</v>
       </c>
-      <c r="D15">
+      <c r="S15">
+        <v>83.33195121951221</v>
+      </c>
+      <c r="T15">
+        <v>0.940538501428935</v>
+      </c>
+      <c r="U15">
+        <v>1.01914191246033</v>
+      </c>
+      <c r="V15">
+        <v>127445000</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1.10895478725433</v>
+      </c>
+      <c r="Y15">
+        <v>1.43588483333588</v>
+      </c>
+      <c r="Z15">
+        <v>1266851401020.24</v>
+      </c>
+      <c r="AA15">
+        <v>14.971877035387</v>
+      </c>
+      <c r="AB15">
+        <v>33.9787686509511</v>
+      </c>
+      <c r="AC15">
         <v>4.038</v>
       </c>
+      <c r="AD15">
+        <v>91.226</v>
+      </c>
+      <c r="AE15">
+        <v>1.10958802700043</v>
+      </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:31">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>4.64162935950068</v>
+      </c>
+      <c r="C16">
+        <v>17.4349512287206</v>
+      </c>
+      <c r="D16">
+        <v>1.74645633118206</v>
+      </c>
+      <c r="E16">
+        <v>1.69021356105804</v>
+      </c>
+      <c r="F16">
+        <v>0.742322049627638</v>
+      </c>
+      <c r="G16">
+        <v>163.286784590149</v>
+      </c>
+      <c r="H16">
+        <v>17.4186553484795</v>
+      </c>
+      <c r="I16">
         <v>0.296205514141889</v>
       </c>
-      <c r="C16">
+      <c r="J16">
+        <v>39555.4120089198</v>
+      </c>
+      <c r="K16">
+        <v>38475.3952461838</v>
+      </c>
+      <c r="L16">
+        <v>0.429381122519686</v>
+      </c>
+      <c r="M16">
+        <v>31.3</v>
+      </c>
+      <c r="N16">
+        <v>1.80541300773621</v>
+      </c>
+      <c r="O16">
+        <v>19.9261773555302</v>
+      </c>
+      <c r="P16">
+        <v>17.5741647729135</v>
+      </c>
+      <c r="Q16">
+        <v>20.0127792201784</v>
+      </c>
+      <c r="R16">
         <v>2.75922671353253</v>
       </c>
-      <c r="D16">
+      <c r="S16">
+        <v>83.5878048780488</v>
+      </c>
+      <c r="T16">
+        <v>0.957800922146808</v>
+      </c>
+      <c r="U16">
+        <v>0.96859735250473</v>
+      </c>
+      <c r="V16">
+        <v>127276000</v>
+      </c>
+      <c r="W16">
+        <v>0.7</v>
+      </c>
+      <c r="X16">
+        <v>1.13797330856323</v>
+      </c>
+      <c r="Y16">
+        <v>1.59787368774414</v>
+      </c>
+      <c r="Z16">
+        <v>1260680310062.82</v>
+      </c>
+      <c r="AA16">
+        <v>14.2124232003685</v>
+      </c>
+      <c r="AB16">
+        <v>37.4314345686579</v>
+      </c>
+      <c r="AC16">
         <v>3.589</v>
       </c>
+      <c r="AD16">
+        <v>91.304</v>
+      </c>
+      <c r="AE16">
+        <v>1.03605246543884</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:31">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>4.7894399258788</v>
+      </c>
+      <c r="C17">
+        <v>24.0975876501944</v>
+      </c>
+      <c r="D17">
+        <v>1.5335999587436</v>
+      </c>
+      <c r="E17">
+        <v>1.52976644039154</v>
+      </c>
+      <c r="F17">
+        <v>3.0702796590698</v>
+      </c>
+      <c r="G17">
+        <v>162.387183817775</v>
+      </c>
+      <c r="H17">
+        <v>17.4367598376529</v>
+      </c>
+      <c r="I17">
         <v>1.56062669680782</v>
       </c>
-      <c r="C17">
+      <c r="J17">
+        <v>40906.594569246</v>
+      </c>
+      <c r="K17">
+        <v>34960.6393843385</v>
+      </c>
+      <c r="L17">
+        <v>1.66846511717627</v>
+      </c>
+      <c r="M17">
+        <v>30.7</v>
+      </c>
+      <c r="N17">
+        <v>1.75316548347473</v>
+      </c>
+      <c r="O17">
+        <v>19.617744139153</v>
+      </c>
+      <c r="P17">
+        <v>16.9738508264281</v>
+      </c>
+      <c r="Q17">
+        <v>17.990648516827</v>
+      </c>
+      <c r="R17">
         <v>0.795279630579784</v>
       </c>
-      <c r="D17">
+      <c r="S17">
+        <v>83.79390243902439</v>
+      </c>
+      <c r="T17">
+        <v>0.947283518613377</v>
+      </c>
+      <c r="U17">
+        <v>1.05422055721283</v>
+      </c>
+      <c r="V17">
+        <v>127141000</v>
+      </c>
+      <c r="W17">
+        <v>0.4</v>
+      </c>
+      <c r="X17">
+        <v>1.20364701747894</v>
+      </c>
+      <c r="Y17">
+        <v>1.48507380485535</v>
+      </c>
+      <c r="Z17">
+        <v>1233097790281.8</v>
+      </c>
+      <c r="AA17">
+        <v>16.8028215906603</v>
+      </c>
+      <c r="AB17">
+        <v>35.4274083544798</v>
+      </c>
+      <c r="AC17">
         <v>3.385</v>
       </c>
+      <c r="AD17">
+        <v>91.381</v>
+      </c>
+      <c r="AE17">
+        <v>0.988048911094666</v>
+      </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:31">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>4.80036978188832</v>
+      </c>
+      <c r="C18">
+        <v>29.2925939129624</v>
+      </c>
+      <c r="D18">
+        <v>1.39676981537012</v>
+      </c>
+      <c r="E18">
+        <v>1.4822438955307</v>
+      </c>
+      <c r="F18">
+        <v>3.93809128404804</v>
+      </c>
+      <c r="G18">
+        <v>163.446906723913</v>
+      </c>
+      <c r="H18">
+        <v>16.0579692360598</v>
+      </c>
+      <c r="I18">
         <v>0.753826745789127</v>
       </c>
-      <c r="C18">
+      <c r="J18">
+        <v>40596.9686628995</v>
+      </c>
+      <c r="K18">
+        <v>39375.4731620781</v>
+      </c>
+      <c r="L18">
+        <v>0.805362824501671</v>
+      </c>
+      <c r="M18">
+        <v>31.8</v>
+      </c>
+      <c r="N18">
+        <v>1.78482556343079</v>
+      </c>
+      <c r="O18">
+        <v>19.6572481017318</v>
+      </c>
+      <c r="P18">
+        <v>16.7112446327333</v>
+      </c>
+      <c r="Q18">
+        <v>15.2522776095286</v>
+      </c>
+      <c r="R18">
         <v>-0.127258844489712</v>
       </c>
-      <c r="D18">
+      <c r="S18">
+        <v>83.9848780487805</v>
+      </c>
+      <c r="T18">
+        <v>0.929516816486597</v>
+      </c>
+      <c r="U18">
+        <v>0.968189001083374</v>
+      </c>
+      <c r="V18">
+        <v>127076000</v>
+      </c>
+      <c r="W18">
+        <v>0.7</v>
+      </c>
+      <c r="X18">
+        <v>1.41657531261444</v>
+      </c>
+      <c r="Y18">
+        <v>1.38373231887817</v>
+      </c>
+      <c r="Z18">
+        <v>1216518779919.68</v>
+      </c>
+      <c r="AA18">
+        <v>16.968973864069</v>
+      </c>
+      <c r="AB18">
+        <v>31.3102468455884</v>
+      </c>
+      <c r="AC18">
         <v>3.132</v>
       </c>
+      <c r="AD18">
+        <v>91.45699999999999</v>
+      </c>
+      <c r="AE18">
+        <v>0.983571171760559</v>
+      </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:31">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>5.00073457446892</v>
+      </c>
+      <c r="C19">
+        <v>31.3672090384603</v>
+      </c>
+      <c r="D19">
+        <v>1.19184799909608</v>
+      </c>
+      <c r="E19">
+        <v>1.48122704029083</v>
+      </c>
+      <c r="F19">
+        <v>4.12036966283801</v>
+      </c>
+      <c r="G19">
+        <v>168.661930703542</v>
+      </c>
+      <c r="H19">
+        <v>17.5914391047836</v>
+      </c>
+      <c r="I19">
         <v>1.67533175173359</v>
       </c>
-      <c r="C19">
+      <c r="J19">
+        <v>41444.2157443912</v>
+      </c>
+      <c r="K19">
+        <v>38834.0529341227</v>
+      </c>
+      <c r="L19">
+        <v>1.75861180168305</v>
+      </c>
+      <c r="M19">
+        <v>31.8</v>
+      </c>
+      <c r="N19">
+        <v>1.57989025115967</v>
+      </c>
+      <c r="O19">
+        <v>19.4117955495929</v>
+      </c>
+      <c r="P19">
+        <v>16.1953485344611</v>
+      </c>
+      <c r="Q19">
+        <v>16.831774467385</v>
+      </c>
+      <c r="R19">
         <v>0.484199796126422</v>
       </c>
-      <c r="D19">
+      <c r="S19">
+        <v>84.099756097561</v>
+      </c>
+      <c r="T19">
+        <v>0.913229492309334</v>
+      </c>
+      <c r="U19">
+        <v>1.10012805461884</v>
+      </c>
+      <c r="V19">
+        <v>126972000</v>
+      </c>
+      <c r="W19">
+        <v>0.6</v>
+      </c>
+      <c r="X19">
+        <v>1.36364352703094</v>
+      </c>
+      <c r="Y19">
+        <v>1.52945506572723</v>
+      </c>
+      <c r="Z19">
+        <v>1264140980383.63</v>
+      </c>
+      <c r="AA19">
+        <v>16.273309373505</v>
+      </c>
+      <c r="AB19">
+        <v>34.4232135721686</v>
+      </c>
+      <c r="AC19">
         <v>2.822</v>
       </c>
+      <c r="AD19">
+        <v>91.535</v>
+      </c>
+      <c r="AE19">
+        <v>1.00365543365479</v>
+      </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:31">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>5.18448847879524</v>
+      </c>
+      <c r="C20">
+        <v>32.6255246339355</v>
+      </c>
+      <c r="D20">
+        <v>1.07338670657475</v>
+      </c>
+      <c r="E20">
+        <v>1.38858759403229</v>
+      </c>
+      <c r="F20">
+        <v>3.51661817468288</v>
+      </c>
+      <c r="G20">
+        <v>168.035145781732</v>
+      </c>
+      <c r="H20">
+        <v>18.3149455985223</v>
+      </c>
+      <c r="I20">
         <v>0.643391023533141</v>
       </c>
-      <c r="C20">
+      <c r="J20">
+        <v>42141.9352987758</v>
+      </c>
+      <c r="K20">
+        <v>39751.1330982711</v>
+      </c>
+      <c r="L20">
+        <v>0.771168471505248</v>
+      </c>
+      <c r="M20">
+        <v>32.9</v>
+      </c>
+      <c r="N20">
+        <v>1.63458871841431</v>
+      </c>
+      <c r="O20">
+        <v>19.5636743323798</v>
+      </c>
+      <c r="P20">
+        <v>16.0713191758764</v>
+      </c>
+      <c r="Q20">
+        <v>18.2949862035848</v>
+      </c>
+      <c r="R20">
         <v>0.989094598021811</v>
       </c>
-      <c r="D20">
+      <c r="S20">
+        <v>84.2109756097561</v>
+      </c>
+      <c r="T20">
+        <v>0.962497356862304</v>
+      </c>
+      <c r="U20">
+        <v>1.03756272792816</v>
+      </c>
+      <c r="V20">
+        <v>126811000</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1.33422780036926</v>
+      </c>
+      <c r="Y20">
+        <v>1.49385368824005</v>
+      </c>
+      <c r="Z20">
+        <v>1270467038786.78</v>
+      </c>
+      <c r="AA20">
+        <v>14.689130719455</v>
+      </c>
+      <c r="AB20">
+        <v>36.609931802107</v>
+      </c>
+      <c r="AC20">
         <v>2.467</v>
       </c>
+      <c r="AD20">
+        <v>91.616</v>
+      </c>
+      <c r="AE20">
+        <v>0.994713246822357</v>
+      </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:31">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>5.11421002181152</v>
+      </c>
+      <c r="C21">
+        <v>32.3335717535477</v>
+      </c>
+      <c r="D21">
+        <v>1.11143560418892</v>
+      </c>
+      <c r="E21">
+        <v>1.4309983253479</v>
+      </c>
+      <c r="F21">
+        <v>3.45076611445328</v>
+      </c>
+      <c r="G21">
+        <v>176.790357885167</v>
+      </c>
+      <c r="H21">
+        <v>17.4635264275221</v>
+      </c>
+      <c r="I21">
         <v>-0.402169200894946</v>
       </c>
-      <c r="C21">
+      <c r="J21">
+        <v>42678.1511448354</v>
+      </c>
+      <c r="K21">
+        <v>40415.9567649547</v>
+      </c>
+      <c r="L21">
+        <v>-0.262170828573062</v>
+      </c>
+      <c r="M21">
+        <v>33</v>
+      </c>
+      <c r="N21">
+        <v>1.55003654956818</v>
+      </c>
+      <c r="O21">
+        <v>19.9451059201578</v>
+      </c>
+      <c r="P21">
+        <v>16.4238978704123</v>
+      </c>
+      <c r="Q21">
+        <v>17.7528916808924</v>
+      </c>
+      <c r="R21">
         <v>0.468776159383928</v>
       </c>
-      <c r="D21">
+      <c r="S21">
+        <v>84.35634146341459</v>
+      </c>
+      <c r="T21">
+        <v>0.99223146563367</v>
+      </c>
+      <c r="U21">
+        <v>1.01981234550476</v>
+      </c>
+      <c r="V21">
+        <v>126633000</v>
+      </c>
+      <c r="W21">
+        <v>1.2</v>
+      </c>
+      <c r="X21">
+        <v>1.31464898586273</v>
+      </c>
+      <c r="Y21">
+        <v>1.49643456935883</v>
+      </c>
+      <c r="Z21">
+        <v>1322443255598.64</v>
+      </c>
+      <c r="AA21">
+        <v>15.4233523008405</v>
+      </c>
+      <c r="AB21">
+        <v>35.2164181084145</v>
+      </c>
+      <c r="AC21">
         <v>2.351</v>
       </c>
+      <c r="AD21">
+        <v>91.69799999999999</v>
+      </c>
+      <c r="AE21">
+        <v>0.929692089557648</v>
+      </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:31">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>4.73325903501669</v>
+      </c>
+      <c r="C22">
+        <v>38.074669746355</v>
+      </c>
+      <c r="D22">
+        <v>1.13897924015799</v>
+      </c>
+      <c r="E22">
+        <v>1.4637143611908</v>
+      </c>
+      <c r="F22">
+        <v>2.96847858242384</v>
+      </c>
+      <c r="G22">
+        <v>195.201446874432</v>
+      </c>
+      <c r="H22">
+        <v>15.5331828643222</v>
+      </c>
+      <c r="I22">
         <v>-4.16876457146743</v>
       </c>
-      <c r="C22">
+      <c r="J22">
+        <v>42425.6946789651</v>
+      </c>
+      <c r="K22">
+        <v>40028.7341726762</v>
+      </c>
+      <c r="L22">
+        <v>-3.88641911578898</v>
+      </c>
+      <c r="M22">
+        <v>32.3</v>
+      </c>
+      <c r="N22">
+        <v>1.5473005771637</v>
+      </c>
+      <c r="O22">
+        <v>20.9756766472836</v>
+      </c>
+      <c r="P22">
+        <v>23.6059009054084</v>
+      </c>
+      <c r="Q22">
+        <v>15.8020257724508</v>
+      </c>
+      <c r="R22">
         <v>-0.024995834027682</v>
       </c>
-      <c r="D22">
+      <c r="S22">
+        <v>84.56</v>
+      </c>
+      <c r="T22">
+        <v>1.01744793009109</v>
+      </c>
+      <c r="U22">
+        <v>1.02614521980286</v>
+      </c>
+      <c r="V22">
+        <v>126261000</v>
+      </c>
+      <c r="W22">
+        <v>1.2</v>
+      </c>
+      <c r="X22">
+        <v>1.3470870256424</v>
+      </c>
+      <c r="Y22">
+        <v>1.47148048877716</v>
+      </c>
+      <c r="Z22">
+        <v>1390808939303.36</v>
+      </c>
+      <c r="AA22">
+        <v>18.5186166099083</v>
+      </c>
+      <c r="AB22">
+        <v>31.335208636773</v>
+      </c>
+      <c r="AC22">
         <v>2.809</v>
       </c>
+      <c r="AD22">
+        <v>91.782</v>
+      </c>
+      <c r="AE22">
+        <v>0.9829003214836119</v>
+      </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:31">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>4.76899104204118</v>
+      </c>
+      <c r="C23">
+        <v>40.6480738961937</v>
+      </c>
+      <c r="D23">
+        <v>1.22751856952344</v>
+      </c>
+      <c r="E23">
+        <v>1.53576052188873</v>
+      </c>
+      <c r="F23">
+        <v>3.89996604353179</v>
+      </c>
+      <c r="G23">
+        <v>195.272084840154</v>
+      </c>
+      <c r="H23">
+        <v>18.1091919388618</v>
+      </c>
+      <c r="I23">
         <v>2.69657404187188</v>
       </c>
-      <c r="C23">
+      <c r="J23">
+        <v>44355.3487163354</v>
+      </c>
+      <c r="K23">
+        <v>40094.5599795288</v>
+      </c>
+      <c r="L23">
+        <v>3.17001738751661</v>
+      </c>
+      <c r="N23">
+        <v>1.36116814613342</v>
+      </c>
+      <c r="O23">
+        <v>21.2457665716874</v>
+      </c>
+      <c r="P23">
+        <v>21.6186499931383</v>
+      </c>
+      <c r="Q23">
+        <v>18.629254289208</v>
+      </c>
+      <c r="R23">
         <v>-0.23335277939831</v>
       </c>
-      <c r="D23">
+      <c r="S23">
+        <v>84.4456097560976</v>
+      </c>
+      <c r="T23">
+        <v>1.01701079290561</v>
+      </c>
+      <c r="U23">
+        <v>1.0155017375946</v>
+      </c>
+      <c r="V23">
+        <v>125681593</v>
+      </c>
+      <c r="X23">
+        <v>1.36984014511108</v>
+      </c>
+      <c r="Y23">
+        <v>1.54032814502716</v>
+      </c>
+      <c r="Z23">
+        <v>1405748991418.92</v>
+      </c>
+      <c r="AA23">
+        <v>16.0722158274857</v>
+      </c>
+      <c r="AB23">
+        <v>36.7384462280698</v>
+      </c>
+      <c r="AC23">
         <v>2.828</v>
       </c>
+      <c r="AD23">
+        <v>91.867</v>
+      </c>
+      <c r="AE23">
+        <v>1.06584024429321</v>
+      </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:31">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>4.067677427737</v>
+      </c>
+      <c r="C24">
+        <v>35.8692282987228</v>
+      </c>
+      <c r="D24">
+        <v>1.23401036286557</v>
+      </c>
+      <c r="E24">
+        <v>1.53992962837219</v>
+      </c>
+      <c r="F24">
+        <v>2.11637961936876</v>
+      </c>
+      <c r="G24">
+        <v>194.922445076413</v>
+      </c>
+      <c r="H24">
+        <v>21.5464241239166</v>
+      </c>
+      <c r="I24">
         <v>0.941998775483285</v>
       </c>
-      <c r="C24">
+      <c r="J24">
+        <v>47395.8391565645</v>
+      </c>
+      <c r="K24">
+        <v>34065.6438962526</v>
+      </c>
+      <c r="L24">
+        <v>1.39102754851621</v>
+      </c>
+      <c r="N24">
+        <v>1.61941540241241</v>
+      </c>
+      <c r="O24">
+        <v>21.5663525457355</v>
+      </c>
+      <c r="P24">
+        <v>20.9311943137094</v>
+      </c>
+      <c r="Q24">
+        <v>25.2665627129772</v>
+      </c>
+      <c r="R24">
         <v>2.49770278172251</v>
       </c>
-      <c r="D24">
+      <c r="S24">
+        <v>83.99634146341459</v>
+      </c>
+      <c r="T24">
+        <v>1.10588643022492</v>
+      </c>
+      <c r="U24">
+        <v>1.0326372385025</v>
+      </c>
+      <c r="V24">
+        <v>125124989</v>
+      </c>
+      <c r="X24">
+        <v>1.43877255916595</v>
+      </c>
+      <c r="Y24">
+        <v>1.55796921253204</v>
+      </c>
+      <c r="Z24">
+        <v>1227573263129.26</v>
+      </c>
+      <c r="AA24">
+        <v>12.3368757899622</v>
+      </c>
+      <c r="AB24">
+        <v>46.8129868368938</v>
+      </c>
+      <c r="AC24">
         <v>2.6</v>
       </c>
+      <c r="AD24">
+        <v>91.955</v>
+      </c>
+      <c r="AE24">
+        <v>1.02100276947021</v>
+      </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:31">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
-      <c r="B25">
+      <c r="C25">
+        <v>37.2282842764104</v>
+      </c>
+      <c r="E25">
+        <v>1.3956606388092</v>
+      </c>
+      <c r="F25">
+        <v>3.71672795030717</v>
+      </c>
+      <c r="G25">
+        <v>193.694929571516</v>
+      </c>
+      <c r="H25">
+        <v>21.8515912402593</v>
+      </c>
+      <c r="I25">
         <v>1.47503481053384</v>
       </c>
-      <c r="C25">
+      <c r="J25">
+        <v>49896.6436902018</v>
+      </c>
+      <c r="K25">
+        <v>33836.1756271617</v>
+      </c>
+      <c r="L25">
+        <v>1.97080161121153</v>
+      </c>
+      <c r="N25">
+        <v>1.63126504421234</v>
+      </c>
+      <c r="Q25">
+        <v>23.2992883238654</v>
+      </c>
+      <c r="R25">
         <v>3.26813365933164</v>
       </c>
-      <c r="D25">
+      <c r="S25">
+        <v>84.0412195121951</v>
+      </c>
+      <c r="T25">
+        <v>1.19606991540042</v>
+      </c>
+      <c r="U25">
+        <v>0.951136231422424</v>
+      </c>
+      <c r="V25">
+        <v>124516650</v>
+      </c>
+      <c r="X25">
+        <v>1.46932590007782</v>
+      </c>
+      <c r="Y25">
+        <v>1.53553938865662</v>
+      </c>
+      <c r="Z25">
+        <v>1294636035263.82</v>
+      </c>
+      <c r="AA25">
+        <v>13.5181230511633</v>
+      </c>
+      <c r="AB25">
+        <v>45.1508795641248</v>
+      </c>
+      <c r="AC25">
         <v>2.6</v>
       </c>
+      <c r="AD25">
+        <v>92.04300000000001</v>
+      </c>
+      <c r="AE25">
+        <v>1.10550534725189</v>
+      </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:31">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="C26">
+        <v>35.5774040048587</v>
+      </c>
+      <c r="F26">
+        <v>4.82480926257698</v>
+      </c>
+      <c r="G26">
+        <v>195.816206747063</v>
+      </c>
+      <c r="I26">
         <v>0.0836985643852159</v>
       </c>
-      <c r="C26">
+      <c r="J26">
+        <v>51685.038752551</v>
+      </c>
+      <c r="K26">
+        <v>32475.8924992191</v>
+      </c>
+      <c r="L26">
+        <v>0.520666034926037</v>
+      </c>
+      <c r="R26">
         <v>2.73853681635243</v>
       </c>
-      <c r="D26">
+      <c r="V26">
+        <v>123975371</v>
+      </c>
+      <c r="Z26">
+        <v>1230666979042.45</v>
+      </c>
+      <c r="AA26">
+        <v>13.0480484378508</v>
+      </c>
+      <c r="AC26">
         <v>2.563</v>
+      </c>
+      <c r="AD26">
+        <v>92.134</v>
       </c>
     </row>
   </sheetData>

--- a/JPN_WB_timeseries.xlsx
+++ b/JPN_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
   </si>
   <si>
+    <t>GDP (current US$)</t>
+  </si>
+  <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
@@ -38,6 +41,9 @@
   </si>
   <si>
     <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
   </si>
   <si>
     <t>Government expenditure (% of GDP)</t>
@@ -428,12 +434,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -489,8 +495,14 @@
       <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -504,28 +516,34 @@
         <v>50774904690</v>
       </c>
       <c r="G2">
+        <v>3185904656663.85</v>
+      </c>
+      <c r="H2">
         <v>4.84092905699353</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>25801.3950393094</v>
       </c>
-      <c r="J2">
+      <c r="K2">
+        <v>13.3193263921511</v>
+      </c>
+      <c r="L2">
         <v>13.846234221868</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>9.285617818181899</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>3.0785162869516</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>87828344748.00101</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>19.3357137329228</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:21">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -539,34 +557,40 @@
         <v>31638296450</v>
       </c>
       <c r="G3">
+        <v>3648065760648.88</v>
+      </c>
+      <c r="H3">
         <v>3.52335723553459</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>29428.4289039469</v>
       </c>
       <c r="K3">
+        <v>13.3603123526588</v>
+      </c>
+      <c r="M3">
         <v>21.1996323299735</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>8.14327654064587</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>3.25143848753308</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>12.9040620944778</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>80625862247.21609</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>17.7594512543168</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>2.059</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:21">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -580,34 +604,40 @@
         <v>17304245530</v>
       </c>
       <c r="G4">
+        <v>3980702922117.66</v>
+      </c>
+      <c r="H4">
         <v>0.900586066438109</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>31992.7902119161</v>
       </c>
       <c r="K4">
+        <v>13.7426283498214</v>
+      </c>
+      <c r="M4">
         <v>19.6697008813848</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>7.49978379930863</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>1.76028306059271</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>11.4171816474572</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>79696681098.04089</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>17.018068824019</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>2.158</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:21">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -621,34 +651,40 @@
         <v>13913020020</v>
       </c>
       <c r="G5">
+        <v>4536940479038.25</v>
+      </c>
+      <c r="H5">
         <v>-0.459219716250544</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>36345.2441262708</v>
       </c>
       <c r="K5">
+        <v>14.3483678224167</v>
+      </c>
+      <c r="M5">
         <v>19.7501356794817</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>6.80942513525332</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>1.24304589707924</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>11.3792369362166</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>107988991686.206</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>15.7233391305175</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>2.539</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:21">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -662,31 +698,37 @@
         <v>18120890730</v>
       </c>
       <c r="G6">
+        <v>4998797547740.97</v>
+      </c>
+      <c r="H6">
         <v>1.0833831743207</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>39933.5150564874</v>
       </c>
-      <c r="J6">
+      <c r="K6">
+        <v>14.7483119048313</v>
+      </c>
+      <c r="L6">
         <v>15.0271835238702</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>6.97047910606066</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>0.695458057868984</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>135145568170.879</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>15.8103062322757</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>2.89</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:21">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -700,31 +742,37 @@
         <v>22630332260</v>
       </c>
       <c r="G7">
+        <v>5545563663889.7</v>
+      </c>
+      <c r="H7">
         <v>2.6309996164206</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>44197.6191013908</v>
       </c>
-      <c r="J7">
+      <c r="K7">
+        <v>15.079728572976</v>
+      </c>
+      <c r="L7">
         <v>15.0254930135052</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>7.57363450140765</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>-0.127899045020453</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>192619707815.154</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>16.3901049340172</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>3.15</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:21">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -744,37 +792,43 @@
         <v>26402490800.3516</v>
       </c>
       <c r="G8">
+        <v>4923391533851.63</v>
+      </c>
+      <c r="H8">
         <v>3.13387099272759</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>39150.0396308089</v>
       </c>
-      <c r="J8">
+      <c r="K8">
+        <v>15.1459373245418</v>
+      </c>
+      <c r="L8">
         <v>14.9490787342868</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>8.93812314202219</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>0.136600358575942</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>1.16188979148865</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>225593968189.507</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>5.41194184014077</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>18.2538682255522</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>3.383</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:21">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -791,34 +845,40 @@
         <v>23987192131.3981</v>
       </c>
       <c r="G9">
+        <v>4492448605638.94</v>
+      </c>
+      <c r="H9">
         <v>0.981228732290873</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>35638.2319556941</v>
       </c>
-      <c r="J9">
+      <c r="K9">
+        <v>15.3019416593352</v>
+      </c>
+      <c r="L9">
         <v>14.431030048272</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>9.39982198359144</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>1.74780458692129</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>226679071029.627</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>5.67928011600089</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>19.7835176233669</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>3.374</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:21">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -838,37 +898,43 @@
         <v>19805092207.5048</v>
       </c>
       <c r="G10">
+        <v>4098362709531.24</v>
+      </c>
+      <c r="H10">
         <v>-1.27033049466078</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>32423.7556133801</v>
       </c>
-      <c r="J10">
+      <c r="K10">
+        <v>15.6654067661838</v>
+      </c>
+      <c r="L10">
         <v>20.1145615989938</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>8.629380123743379</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>0.661974191385939</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>1.24767482280731</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>222443261241.454</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>6.60815287311936</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>19.0031862223377</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>4.078</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:21">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -885,34 +951,40 @@
         <v>24261868314.2843</v>
       </c>
       <c r="G11">
+        <v>4635982224063.88</v>
+      </c>
+      <c r="H11">
         <v>-0.333929957687772</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>36610.1683163197</v>
       </c>
-      <c r="J11">
+      <c r="K11">
+        <v>16.216773574862</v>
+      </c>
+      <c r="L11">
         <v>17.3108900923912</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>8.320091715130889</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>-0.341296928327602</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>293948150986.321</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>8.247849818430931</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>18.1256307166911</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>4.677</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:21">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -932,37 +1004,43 @@
         <v>45027492991.1547</v>
       </c>
       <c r="G12">
+        <v>4968359075956.59</v>
+      </c>
+      <c r="H12">
         <v>2.76464755136783</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>39169.3595701504</v>
       </c>
-      <c r="J12">
+      <c r="K12">
+        <v>16.549191407008</v>
+      </c>
+      <c r="L12">
         <v>17.1095576406981</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>9.09887738115494</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>-0.67657868359508</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>1.19755268096924</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>361639097011.665</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>8.79520531144647</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>19.5623715839054</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>4.748</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:21">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -979,34 +1057,40 @@
         <v>35660387815.1318</v>
       </c>
       <c r="G13">
+        <v>4374711694090.87</v>
+      </c>
+      <c r="H13">
         <v>0.386103426142029</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>34406.1824638092</v>
       </c>
-      <c r="J13">
+      <c r="K13">
+        <v>17.2289905143177</v>
+      </c>
+      <c r="L13">
         <v>16.2333992095233</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>9.48280450872269</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>-0.740055504162812</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>401957624245.241</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>10.694240054348</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>19.5596044720071</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>5.02</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:21">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1026,37 +1110,43 @@
         <v>30901752305.0355</v>
       </c>
       <c r="G14">
+        <v>4182846045873.61</v>
+      </c>
+      <c r="H14">
         <v>0.0419624992862282</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>32820.7936433254</v>
       </c>
-      <c r="J14">
+      <c r="K14">
+        <v>17.7749067788644</v>
+      </c>
+      <c r="L14">
         <v>16.1070602104528</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>9.5916764589296</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>-0.923494026942286</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>1.17602252960205</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>469618129427.641</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
         <v>13.0738264108092</v>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>20.4471220661583</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>5.386</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:21">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1076,37 +1166,43 @@
         <v>34464575323.9372</v>
       </c>
       <c r="G15">
+        <v>4519561645253.53</v>
+      </c>
+      <c r="H15">
         <v>1.53512549946694</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>35387.0374203599</v>
       </c>
-      <c r="J15">
+      <c r="K15">
+        <v>17.8364695899716</v>
+      </c>
+      <c r="L15">
         <v>15.7293776764486</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>9.860323691152489</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>-0.25654181631606</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>1.0271201133728</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>673554461758.647</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>17.0649282535659</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>21.3261252678119</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>5.251</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:21">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1126,37 +1222,43 @@
         <v>40613733179.7035</v>
       </c>
       <c r="G16">
+        <v>4893116005656.56</v>
+      </c>
+      <c r="H16">
         <v>2.18611569439318</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>38298.9801712303</v>
       </c>
-      <c r="J16">
+      <c r="K16">
+        <v>17.7233548337375</v>
+      </c>
+      <c r="L16">
         <v>15.0737560136373</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>10.8780887981112</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-0.008573388203060431</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>1.02831530570984</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>844667163385.489</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>17.9567856611529</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>23.6643534228975</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>4.734</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:21">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1176,37 +1278,43 @@
         <v>51665013692.5647</v>
       </c>
       <c r="G17">
+        <v>4831467035389.8</v>
+      </c>
+      <c r="H17">
         <v>1.80390087215821</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>37812.8950199948</v>
       </c>
-      <c r="J17">
+      <c r="K17">
+        <v>17.7438933244397</v>
+      </c>
+      <c r="L17">
         <v>15.0518407348066</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>12.4140588557406</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-0.282946068764429</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>1.03576946258545</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>846895906145.13</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>15.8351701910594</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>26.2299545778565</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>4.446</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:21">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1226,37 +1334,43 @@
         <v>58152476830.2043</v>
       </c>
       <c r="G18">
+        <v>4601663122649.92</v>
+      </c>
+      <c r="H18">
         <v>1.3723501275831</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>35991.546002862</v>
       </c>
-      <c r="J18">
+      <c r="K18">
+        <v>17.595075361072</v>
+      </c>
+      <c r="L18">
         <v>14.8453333163917</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>14.3590020520575</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>0.249355116079105</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>1.13833451271057</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>895321278049.835</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>15.0181261034339</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>30.0163760986692</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>4.192</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:21">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1276,37 +1390,43 @@
         <v>72989689116.7238</v>
       </c>
       <c r="G19">
+        <v>4579750920354.81</v>
+      </c>
+      <c r="H19">
         <v>1.48396941157472</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>35779.0245416427</v>
       </c>
-      <c r="J19">
+      <c r="K19">
+        <v>17.6343087480996</v>
+      </c>
+      <c r="L19">
         <v>14.0037943063894</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>15.5274506811561</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>0.0600394544986545</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>1.01037454605103</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>973296740492.651</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>15.0050233221166</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>32.816578051879</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>3.888</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:21">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1326,40 +1446,46 @@
         <v>113643633547.594</v>
       </c>
       <c r="G20">
+        <v>5106679115127.3</v>
+      </c>
+      <c r="H20">
         <v>-1.22428900061713</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>39876.3039685725</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>34.6</v>
       </c>
-      <c r="J20">
+      <c r="K20">
+        <v>18.025030322619</v>
+      </c>
+      <c r="L20">
         <v>15.2644121011595</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>16.8939331648175</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>1.38007886164926</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>0.894625246524811</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>1030762755205.19</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>13.3310524110076</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>34.1294765412245</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>4.002</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:21">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1379,40 +1505,46 @@
         <v>73677116859.5416</v>
       </c>
       <c r="G21">
+        <v>5289493117993.89</v>
+      </c>
+      <c r="H21">
         <v>-5.69323635892741</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>41308.9968370512</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>33</v>
       </c>
-      <c r="J21">
+      <c r="K21">
+        <v>19.3337393097808</v>
+      </c>
+      <c r="L21">
         <v>18.2117006884089</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>11.9706007858756</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>-1.35283672951723</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>0.976251900196075</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>1051654952502.29</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>18.3847316266499</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>24.3901665338555</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>5.068</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:21">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1432,40 +1564,46 @@
         <v>79656513836.629</v>
       </c>
       <c r="G22">
+        <v>5759071769013.11</v>
+      </c>
+      <c r="H22">
         <v>4.09791791943181</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>44968.1562349739</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>31.5</v>
       </c>
-      <c r="J22">
+      <c r="K22">
+        <v>19.2025962424431</v>
+      </c>
+      <c r="L22">
         <v>17.2217468141394</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>13.5799692441961</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>-0.7282432075177659</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>0.879353165626526</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>1104563760972.06</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>15.8070134520484</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>28.4984726938389</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>5.102</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:21">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1485,40 +1623,46 @@
         <v>116835198104.238</v>
       </c>
       <c r="G23">
+        <v>6233147172341.35</v>
+      </c>
+      <c r="H23">
         <v>0.0238095237995424</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>48760.0789494211</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>33</v>
       </c>
-      <c r="J23">
+      <c r="K23">
+        <v>19.885399284228</v>
+      </c>
+      <c r="L23">
         <v>18.5956788727445</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>15.4204984672798</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>-0.272455616101245</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>0.99509197473526</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>1295838676317.29</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>15.2333155611711</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>30.1949607286296</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>4.55</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:21">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1538,40 +1682,46 @@
         <v>117632352926.831</v>
       </c>
       <c r="G24">
+        <v>6272362996105.03</v>
+      </c>
+      <c r="H24">
         <v>1.37475099905274</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>49145.2804308193</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>32.5</v>
       </c>
-      <c r="J24">
+      <c r="K24">
+        <v>19.9573325085164</v>
+      </c>
+      <c r="L24">
         <v>18.1117047475127</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>16.0561363041928</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>-0.0440645104432608</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>0.948442876338959</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>1268085524238.3</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>14.2347343263613</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>30.4709109171752</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>4.358</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:21">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1591,40 +1741,46 @@
         <v>155684602276.7</v>
       </c>
       <c r="G25">
+        <v>5212328181166.18</v>
+      </c>
+      <c r="H25">
         <v>2.00510017681211</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>40898.6478964744</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>31.5</v>
       </c>
-      <c r="J25">
+      <c r="K25">
+        <v>19.854370134417</v>
+      </c>
+      <c r="L25">
         <v>18.1406509054638</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>18.1946119190738</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>0.335037912184772</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>1.01914191246033</v>
       </c>
-      <c r="P25">
+      <c r="R25">
         <v>1266851401020.24</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>14.971877035387</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>33.9787686509511</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>4.038</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:21">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -1644,40 +1800,46 @@
         <v>137924439219.3</v>
       </c>
       <c r="G26">
+        <v>4896994405353.29</v>
+      </c>
+      <c r="H26">
         <v>0.296205514141889</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>38475.3952461838</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>31.3</v>
       </c>
-      <c r="J26">
+      <c r="K26">
+        <v>19.9261773555302</v>
+      </c>
+      <c r="L26">
         <v>17.5741647729135</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>20.0127792201784</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2.75922671353253</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>0.96859735250473</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>1260680310062.82</v>
       </c>
-      <c r="Q26">
+      <c r="S26">
         <v>14.2124232003685</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>37.4314345686579</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>3.589</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:21">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -1697,40 +1859,46 @@
         <v>138415009626.674</v>
       </c>
       <c r="G27">
+        <v>4444930651964.18</v>
+      </c>
+      <c r="H27">
         <v>1.56062669680782</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>34960.6393843385</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>30.7</v>
       </c>
-      <c r="J27">
+      <c r="K27">
+        <v>19.617744139153</v>
+      </c>
+      <c r="L27">
         <v>16.9738508264281</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>17.990648516827</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>0.795279630579784</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>1.05422055721283</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>1233097790281.8</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>16.8028215906603</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>35.4274083544798</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>3.385</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:21">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -1750,40 +1918,46 @@
         <v>178610388912.655</v>
       </c>
       <c r="G28">
+        <v>5003677627544.24</v>
+      </c>
+      <c r="H28">
         <v>0.753826745789127</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>39375.4731620781</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>31.8</v>
       </c>
-      <c r="J28">
+      <c r="K28">
+        <v>19.6572481017318</v>
+      </c>
+      <c r="L28">
         <v>16.7112446327333</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>15.2522776095286</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>-0.127258844489712</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>0.968189001083374</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>1216518779919.68</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>16.968973864069</v>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>31.3102468455884</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>3.132</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:21">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -1803,40 +1977,46 @@
         <v>173750236904.08</v>
       </c>
       <c r="G29">
+        <v>4930837369151.42</v>
+      </c>
+      <c r="H29">
         <v>1.67533175173359</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>38834.0529341227</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>31.8</v>
       </c>
-      <c r="J29">
+      <c r="K29">
+        <v>19.4117955495929</v>
+      </c>
+      <c r="L29">
         <v>16.1953485344611</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>16.831774467385</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>0.484199796126422</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>1.10012805461884</v>
       </c>
-      <c r="P29">
+      <c r="R29">
         <v>1264140980383.63</v>
       </c>
-      <c r="Q29">
+      <c r="S29">
         <v>16.273309373505</v>
       </c>
-      <c r="R29">
+      <c r="T29">
         <v>34.4232135721686</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>2.822</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:21">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -1856,40 +2036,46 @@
         <v>160218306051.633</v>
       </c>
       <c r="G30">
+        <v>5040880939324.86</v>
+      </c>
+      <c r="H30">
         <v>0.643391023533141</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>39751.1330982711</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>32.9</v>
       </c>
-      <c r="J30">
+      <c r="K30">
+        <v>19.5636743323798</v>
+      </c>
+      <c r="L30">
         <v>16.0713191758764</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>18.2949862035848</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>0.989094598021811</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>1.03756272792816</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>1270467038786.78</v>
       </c>
-      <c r="Q30">
+      <c r="S30">
         <v>14.689130719455</v>
       </c>
-      <c r="R30">
+      <c r="T30">
         <v>36.609931802107</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>2.467</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:21">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -1909,40 +2095,46 @@
         <v>258284325075.722</v>
       </c>
       <c r="G31">
+        <v>5117993853016.51</v>
+      </c>
+      <c r="H31">
         <v>-0.402169200894946</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>40415.9567649547</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>33</v>
       </c>
-      <c r="J31">
+      <c r="K31">
+        <v>19.9451059201578</v>
+      </c>
+      <c r="L31">
         <v>16.4238978704123</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>17.7528916808924</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>0.468776159383928</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>1.01981234550476</v>
       </c>
-      <c r="P31">
+      <c r="R31">
         <v>1322443255598.64</v>
       </c>
-      <c r="Q31">
+      <c r="S31">
         <v>15.4233523008405</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>35.2164181084145</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>2.351</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:21">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -1962,40 +2154,46 @@
         <v>150118191351.37</v>
       </c>
       <c r="G32">
+        <v>5054068005376.28</v>
+      </c>
+      <c r="H32">
         <v>-4.16876457146743</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>40028.7341726762</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>32.3</v>
       </c>
-      <c r="J32">
+      <c r="K32">
+        <v>20.9756766472836</v>
+      </c>
+      <c r="L32">
         <v>23.6059009054084</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>15.8020257724508</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>-0.024995834027682</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>1.02614521980286</v>
       </c>
-      <c r="P32">
+      <c r="R32">
         <v>1390808939303.36</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>18.5186166099083</v>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>31.335208636773</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>2.809</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:21">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2015,37 +2213,43 @@
         <v>209691839494.071</v>
       </c>
       <c r="G33">
+        <v>5039148168861.22</v>
+      </c>
+      <c r="H33">
         <v>2.69657404187188</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>40094.5599795288</v>
       </c>
-      <c r="J33">
+      <c r="K33">
+        <v>21.2457665716874</v>
+      </c>
+      <c r="L33">
         <v>21.6186499931383</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>18.629254289208</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>-0.23335277939831</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>1.0155017375946</v>
       </c>
-      <c r="P33">
+      <c r="R33">
         <v>1405748991418.92</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>16.0722158274857</v>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>36.7384462280698</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>2.828</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:21">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2065,37 +2269,43 @@
         <v>174943442053.15</v>
       </c>
       <c r="G34">
+        <v>4262463317796.53</v>
+      </c>
+      <c r="H34">
         <v>0.941998775483285</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>34065.6438962526</v>
       </c>
-      <c r="J34">
+      <c r="K34">
+        <v>21.5663525457355</v>
+      </c>
+      <c r="L34">
         <v>20.9311943137094</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>25.2665627129772</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>2.49770278172251</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>1.0326372385025</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>1227573263129.26</v>
       </c>
-      <c r="Q34">
+      <c r="S34">
         <v>12.3368757899622</v>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>46.8129868368938</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>2.6</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:21">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2115,34 +2325,37 @@
         <v>195436741259.747</v>
       </c>
       <c r="G35">
+        <v>4213167237905.83</v>
+      </c>
+      <c r="H35">
         <v>1.47503481053384</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>33836.1756271617</v>
       </c>
-      <c r="L35">
+      <c r="N35">
         <v>23.2992883238654</v>
       </c>
-      <c r="M35">
+      <c r="O35">
         <v>3.26813365933164</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>0.951136231422424</v>
       </c>
-      <c r="P35">
+      <c r="R35">
         <v>1294636035263.82</v>
       </c>
-      <c r="Q35">
+      <c r="S35">
         <v>13.5181230511633</v>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>45.1508795641248</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>2.6</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:21">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2156,21 +2369,24 @@
         <v>208220716289.443</v>
       </c>
       <c r="G36">
+        <v>4026210821146.81</v>
+      </c>
+      <c r="H36">
         <v>0.0836985643852159</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>32475.8924992191</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>2.73853681635243</v>
       </c>
-      <c r="P36">
+      <c r="R36">
         <v>1230666979042.45</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
         <v>13.0480484378508</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>2.563</v>
       </c>
     </row>

--- a/JPN_WB_timeseries.xlsx
+++ b/JPN_WB_timeseries.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D6797-99B9-E045-86B3-DA670B36D9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -46,6 +40,9 @@
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
     <t>Trade openness (% of GDP)</t>
   </si>
   <si>
@@ -64,8 +61,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,18 +79,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -123,33 +114,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +169,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,7 +203,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -256,10 +237,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -432,13 +412,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -476,8 +456,11 @@
       <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -485,233 +468,247 @@
         <v>1.22991895675659</v>
       </c>
       <c r="C2">
-        <v>2.6304554890353899</v>
+        <v>2.63045548903539</v>
       </c>
       <c r="D2">
         <v>10.4634942027505</v>
       </c>
       <c r="E2">
-        <v>2.7646475513678301</v>
+        <v>2.76464755136783</v>
       </c>
       <c r="F2">
-        <v>39169.359570150402</v>
+        <v>39169.3595701504</v>
       </c>
       <c r="G2">
         <v>17.1095576406981</v>
       </c>
       <c r="H2">
-        <v>9.0988773811549404</v>
+        <v>9.09887738115494</v>
       </c>
       <c r="I2">
         <v>-0.67657868359508</v>
       </c>
       <c r="J2">
-        <v>19.562371583905399</v>
+        <v>1.19755268096924</v>
       </c>
       <c r="K2">
+        <v>19.5623715839054</v>
+      </c>
+      <c r="L2">
         <v>135.6</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>-7.3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
         <v>1.97087092323799</v>
       </c>
       <c r="D3">
-        <v>10.076799963284399</v>
+        <v>10.0767999632844</v>
       </c>
       <c r="E3">
-        <v>0.38610342614202903</v>
+        <v>0.386103426142029</v>
       </c>
       <c r="F3">
         <v>34406.1824638092</v>
       </c>
       <c r="G3">
-        <v>16.233399209523299</v>
+        <v>16.2333992095233</v>
       </c>
       <c r="H3">
-        <v>9.4828045087226904</v>
+        <v>9.48280450872269</v>
       </c>
       <c r="I3">
-        <v>-0.74005550416281196</v>
-      </c>
-      <c r="J3">
-        <v>19.559604472007099</v>
+        <v>-0.740055504162812</v>
       </c>
       <c r="K3">
+        <v>19.5596044720071</v>
+      </c>
+      <c r="L3">
         <v>145.1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>-6.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>0.93693983554840099</v>
+        <v>0.936939835548401</v>
       </c>
       <c r="C4">
-        <v>2.6025652079499699</v>
+        <v>2.60256520794997</v>
       </c>
       <c r="D4">
-        <v>10.855445607228701</v>
+        <v>10.8554456072287</v>
       </c>
       <c r="E4">
-        <v>4.1962499286228201E-2</v>
+        <v>0.0419624992862282</v>
       </c>
       <c r="F4">
         <v>32820.7936433254</v>
       </c>
       <c r="G4">
-        <v>16.107060210452801</v>
+        <v>16.1070602104528</v>
       </c>
       <c r="H4">
-        <v>9.5916764589295997</v>
+        <v>9.5916764589296</v>
       </c>
       <c r="I4">
-        <v>-0.92349402694228599</v>
+        <v>-0.923494026942286</v>
       </c>
       <c r="J4">
+        <v>1.17602252960205</v>
+      </c>
+      <c r="K4">
         <v>20.4471220661583</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>154.1</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>-7.3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>1.1698737144470199</v>
+        <v>1.16987371444702</v>
       </c>
       <c r="C5">
-        <v>3.0839389081120698</v>
+        <v>3.08393890811207</v>
       </c>
       <c r="D5">
         <v>11.4658015766594</v>
       </c>
       <c r="E5">
-        <v>1.5351254994669401</v>
+        <v>1.53512549946694</v>
       </c>
       <c r="F5">
-        <v>35387.037420359899</v>
+        <v>35387.0374203599</v>
       </c>
       <c r="G5">
         <v>15.7293776764486</v>
       </c>
       <c r="H5">
-        <v>9.8603236911524892</v>
+        <v>9.860323691152489</v>
       </c>
       <c r="I5">
-        <v>-0.25654181631605999</v>
+        <v>-0.25654181631606</v>
       </c>
       <c r="J5">
+        <v>1.0271201133728</v>
+      </c>
+      <c r="K5">
         <v>21.3261252678119</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>160</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>-7.4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>1.2000110149383501</v>
+        <v>1.20001101493835</v>
       </c>
       <c r="C6">
-        <v>3.7193835045858399</v>
+        <v>3.71938350458584</v>
       </c>
       <c r="D6">
-        <v>12.786264624786201</v>
+        <v>12.7862646247862</v>
       </c>
       <c r="E6">
-        <v>2.1861156943931799</v>
+        <v>2.18611569439318</v>
       </c>
       <c r="F6">
-        <v>38298.980171230301</v>
+        <v>38298.9801712303</v>
       </c>
       <c r="G6">
-        <v>15.073756013637301</v>
+        <v>15.0737560136373</v>
       </c>
       <c r="H6">
         <v>10.8780887981112</v>
       </c>
       <c r="I6">
-        <v>-8.5733882030604308E-3</v>
+        <v>-0.008573388203060431</v>
       </c>
       <c r="J6">
-        <v>23.664353422897499</v>
+        <v>1.02831530570984</v>
       </c>
       <c r="K6">
+        <v>23.6643534228975</v>
+      </c>
+      <c r="L6">
         <v>169.5</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>-5.3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>1.2101241350173999</v>
+        <v>1.2101241350174</v>
       </c>
       <c r="C7">
-        <v>3.5211406564056702</v>
+        <v>3.52114065640567</v>
       </c>
       <c r="D7">
-        <v>13.815895722115901</v>
+        <v>13.8158957221159</v>
       </c>
       <c r="E7">
-        <v>1.8039008721582099</v>
+        <v>1.80390087215821</v>
       </c>
       <c r="F7">
-        <v>37812.895019994801</v>
+        <v>37812.8950199948</v>
       </c>
       <c r="G7">
         <v>15.0518407348066</v>
       </c>
       <c r="H7">
-        <v>12.414058855740601</v>
+        <v>12.4140588557406</v>
       </c>
       <c r="I7">
-        <v>-0.28294606876442902</v>
+        <v>-0.282946068764429</v>
       </c>
       <c r="J7">
+        <v>1.03576946258545</v>
+      </c>
+      <c r="K7">
         <v>26.2299545778565</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>174.6</v>
       </c>
-      <c r="L7">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>1.3208487033844001</v>
+        <v>1.3208487033844</v>
       </c>
       <c r="C8">
-        <v>3.7958617286287599</v>
+        <v>3.79586172862876</v>
       </c>
       <c r="D8">
         <v>15.6573740466117</v>
@@ -723,42 +720,45 @@
         <v>35991.546002862</v>
       </c>
       <c r="G8">
-        <v>14.845333316391701</v>
+        <v>14.8453333163917</v>
       </c>
       <c r="H8">
         <v>14.3590020520575</v>
       </c>
       <c r="I8">
-        <v>0.24935511607910499</v>
+        <v>0.249355116079105</v>
       </c>
       <c r="J8">
-        <v>30.016376098669198</v>
+        <v>1.13833451271057</v>
       </c>
       <c r="K8">
+        <v>30.0163760986692</v>
+      </c>
+      <c r="L8">
         <v>174.1</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>1.2302278280258201</v>
+        <v>1.23022782802582</v>
       </c>
       <c r="C9">
-        <v>4.6233004825925503</v>
+        <v>4.62330048259255</v>
       </c>
       <c r="D9">
-        <v>17.289127370722898</v>
+        <v>17.2891273707229</v>
       </c>
       <c r="E9">
         <v>1.48396941157472</v>
       </c>
       <c r="F9">
-        <v>35779.024541642699</v>
+        <v>35779.0245416427</v>
       </c>
       <c r="G9">
         <v>14.0037943063894</v>
@@ -767,57 +767,63 @@
         <v>15.5274506811561</v>
       </c>
       <c r="I9">
-        <v>6.0039454498654499E-2</v>
+        <v>0.0600394544986545</v>
       </c>
       <c r="J9">
-        <v>32.816578051878999</v>
+        <v>1.01037454605103</v>
       </c>
       <c r="K9">
+        <v>32.816578051879</v>
+      </c>
+      <c r="L9">
         <v>173</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>-2.9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>1.3238885402679399</v>
+        <v>1.32388854026794</v>
       </c>
       <c r="C10">
         <v>2.78294234789655</v>
       </c>
       <c r="D10">
-        <v>17.235543376407101</v>
+        <v>17.2355433764071</v>
       </c>
       <c r="E10">
-        <v>-1.2242890006171301</v>
+        <v>-1.22428900061713</v>
       </c>
       <c r="F10">
-        <v>39876.303968572502</v>
+        <v>39876.3039685725</v>
       </c>
       <c r="G10">
         <v>15.2644121011595</v>
       </c>
       <c r="H10">
-        <v>16.893933164817501</v>
+        <v>16.8939331648175</v>
       </c>
       <c r="I10">
-        <v>1.3800788616492601</v>
+        <v>1.38007886164926</v>
       </c>
       <c r="J10">
-        <v>34.129476541224498</v>
+        <v>0.894625246524811</v>
       </c>
       <c r="K10">
+        <v>34.1294765412245</v>
+      </c>
+      <c r="L10">
         <v>180.9</v>
       </c>
-      <c r="L10">
-        <v>-4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -825,13 +831,13 @@
         <v>1.36922454833984</v>
       </c>
       <c r="C11">
-        <v>2.7540958349443501</v>
+        <v>2.75409583494435</v>
       </c>
       <c r="D11">
         <v>12.41956574798</v>
       </c>
       <c r="E11">
-        <v>-5.6932363589274102</v>
+        <v>-5.69323635892741</v>
       </c>
       <c r="F11">
         <v>41308.9968370512</v>
@@ -843,19 +849,22 @@
         <v>11.9706007858756</v>
       </c>
       <c r="I11">
-        <v>-1.3528367295172301</v>
+        <v>-1.35283672951723</v>
       </c>
       <c r="J11">
-        <v>24.390166533855499</v>
+        <v>0.976251900196075</v>
       </c>
       <c r="K11">
+        <v>24.3901665338555</v>
+      </c>
+      <c r="L11">
         <v>198.8</v>
       </c>
-      <c r="L11">
-        <v>-9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M11">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -866,80 +875,86 @@
         <v>3.83547896264376</v>
       </c>
       <c r="D12">
-        <v>14.918503449642801</v>
+        <v>14.9185034496428</v>
       </c>
       <c r="E12">
-        <v>4.0979179194318096</v>
+        <v>4.09791791943181</v>
       </c>
       <c r="F12">
-        <v>44968.156234973903</v>
+        <v>44968.1562349739</v>
       </c>
       <c r="G12">
-        <v>17.221746814139401</v>
+        <v>17.2217468141394</v>
       </c>
       <c r="H12">
         <v>13.5799692441961</v>
       </c>
       <c r="I12">
-        <v>-0.72824320751776594</v>
+        <v>-0.7282432075177659</v>
       </c>
       <c r="J12">
-        <v>28.498472693838899</v>
+        <v>0.879353165626526</v>
       </c>
       <c r="K12">
+        <v>28.4984726938389</v>
+      </c>
+      <c r="L12">
         <v>205.9</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>-9.1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>1.5543754100799601</v>
+        <v>1.55437541007996</v>
       </c>
       <c r="C13">
-        <v>2.0791532884655601</v>
+        <v>2.07915328846556</v>
       </c>
       <c r="D13">
         <v>14.7744622613499</v>
       </c>
       <c r="E13">
-        <v>2.38095237995424E-2</v>
+        <v>0.0238095237995424</v>
       </c>
       <c r="F13">
-        <v>48760.078949421099</v>
+        <v>48760.0789494211</v>
       </c>
       <c r="G13">
         <v>18.5956788727445</v>
       </c>
       <c r="H13">
-        <v>15.420498467279799</v>
+        <v>15.4204984672798</v>
       </c>
       <c r="I13">
-        <v>-0.27245561610124502</v>
+        <v>-0.272455616101245</v>
       </c>
       <c r="J13">
-        <v>30.194960728629599</v>
+        <v>0.99509197473526</v>
       </c>
       <c r="K13">
+        <v>30.1949607286296</v>
+      </c>
+      <c r="L13">
         <v>219.2</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>-9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>1.6189486980438199</v>
+        <v>1.61894869804382</v>
       </c>
       <c r="C14">
-        <v>0.95844261141204001</v>
+        <v>0.95844261141204</v>
       </c>
       <c r="D14">
         <v>14.4147746129824</v>
@@ -948,28 +963,31 @@
         <v>1.37475099905274</v>
       </c>
       <c r="F14">
-        <v>49145.280430819301</v>
+        <v>49145.2804308193</v>
       </c>
       <c r="G14">
         <v>18.1117047475127</v>
       </c>
       <c r="H14">
-        <v>16.056136304192801</v>
+        <v>16.0561363041928</v>
       </c>
       <c r="I14">
-        <v>-4.4064510443260797E-2</v>
+        <v>-0.0440645104432608</v>
       </c>
       <c r="J14">
+        <v>0.948442876338959</v>
+      </c>
+      <c r="K14">
         <v>30.4709109171752</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>226.1</v>
       </c>
-      <c r="L14">
-        <v>-8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14">
+        <v>-8.199999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -977,37 +995,40 @@
         <v>1.6482492685318</v>
       </c>
       <c r="C15">
-        <v>0.88978541580886295</v>
+        <v>0.8897854158088629</v>
       </c>
       <c r="D15">
         <v>15.7841567318773</v>
       </c>
       <c r="E15">
-        <v>2.0051001768121099</v>
+        <v>2.00510017681211</v>
       </c>
       <c r="F15">
-        <v>40898.647896474402</v>
+        <v>40898.6478964744</v>
       </c>
       <c r="G15">
-        <v>18.140650905463801</v>
+        <v>18.1406509054638</v>
       </c>
       <c r="H15">
         <v>18.1946119190738</v>
       </c>
       <c r="I15">
-        <v>0.33503791218477202</v>
+        <v>0.335037912184772</v>
       </c>
       <c r="J15">
-        <v>33.978768650951103</v>
+        <v>1.01914191246033</v>
       </c>
       <c r="K15">
+        <v>33.9787686509511</v>
+      </c>
+      <c r="L15">
         <v>229.5</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>-7.6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -1015,45 +1036,48 @@
         <v>1.69021356105804</v>
       </c>
       <c r="C16">
-        <v>0.74232204962763804</v>
+        <v>0.742322049627638</v>
       </c>
       <c r="D16">
-        <v>17.418655348479501</v>
+        <v>17.4186553484795</v>
       </c>
       <c r="E16">
         <v>0.296205514141889</v>
       </c>
       <c r="F16">
-        <v>38475.395246183798</v>
+        <v>38475.3952461838</v>
       </c>
       <c r="G16">
-        <v>17.574164772913502</v>
+        <v>17.5741647729135</v>
       </c>
       <c r="H16">
-        <v>20.012779220178398</v>
+        <v>20.0127792201784</v>
       </c>
       <c r="I16">
-        <v>2.7592267135325299</v>
+        <v>2.75922671353253</v>
       </c>
       <c r="J16">
-        <v>37.431434568657899</v>
+        <v>0.96859735250473</v>
       </c>
       <c r="K16">
+        <v>37.4314345686579</v>
+      </c>
+      <c r="L16">
         <v>233.3</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>-5.6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>1.5297664403915401</v>
+        <v>1.52976644039154</v>
       </c>
       <c r="C17">
-        <v>3.0702796590697998</v>
+        <v>3.0702796590698</v>
       </c>
       <c r="D17">
         <v>17.4367598376529</v>
@@ -1062,28 +1086,31 @@
         <v>1.56062669680782</v>
       </c>
       <c r="F17">
-        <v>34960.639384338501</v>
+        <v>34960.6393843385</v>
       </c>
       <c r="G17">
-        <v>16.973850826428102</v>
+        <v>16.9738508264281</v>
       </c>
       <c r="H17">
-        <v>17.990648516827001</v>
+        <v>17.990648516827</v>
       </c>
       <c r="I17">
-        <v>0.79527963057978401</v>
+        <v>0.795279630579784</v>
       </c>
       <c r="J17">
-        <v>35.427408354479802</v>
+        <v>1.05422055721283</v>
       </c>
       <c r="K17">
+        <v>35.4274083544798</v>
+      </c>
+      <c r="L17">
         <v>228.3</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>-3.7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -1091,75 +1118,81 @@
         <v>1.4822438955307</v>
       </c>
       <c r="C18">
-        <v>3.9380912840480402</v>
+        <v>3.93809128404804</v>
       </c>
       <c r="D18">
-        <v>16.057969236059801</v>
+        <v>16.0579692360598</v>
       </c>
       <c r="E18">
-        <v>0.75382674578912701</v>
+        <v>0.753826745789127</v>
       </c>
       <c r="F18">
-        <v>39375.473162078102</v>
+        <v>39375.4731620781</v>
       </c>
       <c r="G18">
-        <v>16.711244632733301</v>
+        <v>16.7112446327333</v>
       </c>
       <c r="H18">
-        <v>15.252277609528599</v>
+        <v>15.2522776095286</v>
       </c>
       <c r="I18">
         <v>-0.127258844489712</v>
       </c>
       <c r="J18">
-        <v>31.310246845588399</v>
+        <v>0.968189001083374</v>
       </c>
       <c r="K18">
+        <v>31.3102468455884</v>
+      </c>
+      <c r="L18">
         <v>232.4</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>-3.6</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>1.4812270402908301</v>
+        <v>1.48122704029083</v>
       </c>
       <c r="C19">
-        <v>4.1203696628380104</v>
+        <v>4.12036966283801</v>
       </c>
       <c r="D19">
         <v>17.5914391047836</v>
       </c>
       <c r="E19">
-        <v>1.6753317517335899</v>
+        <v>1.67533175173359</v>
       </c>
       <c r="F19">
-        <v>38834.052934122701</v>
+        <v>38834.0529341227</v>
       </c>
       <c r="G19">
         <v>16.1953485344611</v>
       </c>
       <c r="H19">
-        <v>16.831774467384999</v>
+        <v>16.831774467385</v>
       </c>
       <c r="I19">
         <v>0.484199796126422</v>
       </c>
       <c r="J19">
-        <v>34.423213572168599</v>
+        <v>1.10012805461884</v>
       </c>
       <c r="K19">
+        <v>34.4232135721686</v>
+      </c>
+      <c r="L19">
         <v>231.3</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>-3.1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -1173,74 +1206,80 @@
         <v>18.3149455985223</v>
       </c>
       <c r="E20">
-        <v>0.64339102353314104</v>
+        <v>0.643391023533141</v>
       </c>
       <c r="F20">
-        <v>39751.133098271101</v>
+        <v>39751.1330982711</v>
       </c>
       <c r="G20">
         <v>16.0713191758764</v>
       </c>
       <c r="H20">
-        <v>18.294986203584799</v>
+        <v>18.2949862035848</v>
       </c>
       <c r="I20">
-        <v>0.98909459802181099</v>
+        <v>0.989094598021811</v>
       </c>
       <c r="J20">
-        <v>36.609931802106999</v>
+        <v>1.03756272792816</v>
       </c>
       <c r="K20">
+        <v>36.609931802107</v>
+      </c>
+      <c r="L20">
         <v>232.4</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>-2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>1.4309983253478999</v>
+        <v>1.4309983253479</v>
       </c>
       <c r="C21">
         <v>3.45076611445328</v>
       </c>
       <c r="D21">
-        <v>17.463526427522101</v>
+        <v>17.4635264275221</v>
       </c>
       <c r="E21">
-        <v>-0.40216920089494601</v>
+        <v>-0.402169200894946</v>
       </c>
       <c r="F21">
-        <v>40415.956764954703</v>
+        <v>40415.9567649547</v>
       </c>
       <c r="G21">
-        <v>16.423897870412301</v>
+        <v>16.4238978704123</v>
       </c>
       <c r="H21">
         <v>17.7528916808924</v>
       </c>
       <c r="I21">
-        <v>0.46877615938392803</v>
+        <v>0.468776159383928</v>
       </c>
       <c r="J21">
-        <v>35.216418108414501</v>
+        <v>1.01981234550476</v>
       </c>
       <c r="K21">
+        <v>35.2164181084145</v>
+      </c>
+      <c r="L21">
         <v>236.4</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>-3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>1.4637143611907999</v>
+        <v>1.4637143611908</v>
       </c>
       <c r="C22">
         <v>2.96847858242384</v>
@@ -1249,31 +1288,34 @@
         <v>15.5331828643222</v>
       </c>
       <c r="E22">
-        <v>-4.1687645714674302</v>
+        <v>-4.16876457146743</v>
       </c>
       <c r="F22">
-        <v>40028.734172676202</v>
+        <v>40028.7341726762</v>
       </c>
       <c r="G22">
-        <v>23.605900905408401</v>
+        <v>23.6059009054084</v>
       </c>
       <c r="H22">
-        <v>15.802025772450801</v>
+        <v>15.8020257724508</v>
       </c>
       <c r="I22">
-        <v>-2.4995834027682001E-2</v>
+        <v>-0.024995834027682</v>
       </c>
       <c r="J22">
+        <v>1.02614521980286</v>
+      </c>
+      <c r="K22">
         <v>31.335208636773</v>
       </c>
-      <c r="K22">
-        <v>258.39999999999998</v>
-      </c>
       <c r="L22">
+        <v>258.4</v>
+      </c>
+      <c r="M22">
         <v>-9.1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -1281,80 +1323,86 @@
         <v>1.53576052188873</v>
       </c>
       <c r="C23">
-        <v>3.8999660435317902</v>
+        <v>3.89996604353179</v>
       </c>
       <c r="D23">
-        <v>18.109191938861802</v>
+        <v>18.1091919388618</v>
       </c>
       <c r="E23">
-        <v>2.6965740418718802</v>
+        <v>2.69657404187188</v>
       </c>
       <c r="F23">
         <v>40094.5599795288</v>
       </c>
       <c r="G23">
-        <v>21.618649993138298</v>
+        <v>21.6186499931383</v>
       </c>
       <c r="H23">
-        <v>18.629254289207999</v>
+        <v>18.629254289208</v>
       </c>
       <c r="I23">
-        <v>-0.23335277939831001</v>
+        <v>-0.23335277939831</v>
       </c>
       <c r="J23">
-        <v>36.738446228069797</v>
+        <v>1.0155017375946</v>
       </c>
       <c r="K23">
+        <v>36.7384462280698</v>
+      </c>
+      <c r="L23">
         <v>253.7</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>-6.1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>1.5399296283721899</v>
+        <v>1.53992962837219</v>
       </c>
       <c r="C24">
-        <v>2.1163796193687601</v>
+        <v>2.11637961936876</v>
       </c>
       <c r="D24">
-        <v>21.546424123916601</v>
+        <v>21.5464241239166</v>
       </c>
       <c r="E24">
-        <v>0.94199877548328503</v>
+        <v>0.941998775483285</v>
       </c>
       <c r="F24">
-        <v>34065.643896252601</v>
+        <v>34065.6438962526</v>
       </c>
       <c r="G24">
-        <v>20.931194313709401</v>
+        <v>20.9311943137094</v>
       </c>
       <c r="H24">
-        <v>25.266562712977201</v>
+        <v>25.2665627129772</v>
       </c>
       <c r="I24">
-        <v>2.4977027817225101</v>
+        <v>2.49770278172251</v>
       </c>
       <c r="J24">
-        <v>46.812986836893799</v>
+        <v>1.0326372385025</v>
       </c>
       <c r="K24">
+        <v>46.8129868368938</v>
+      </c>
+      <c r="L24">
         <v>248.2</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>-4.2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>1.3956606388092001</v>
+        <v>1.3956606388092</v>
       </c>
       <c r="C25">
         <v>3.71672795030717</v>
@@ -1366,50 +1414,47 @@
         <v>1.47503481053384</v>
       </c>
       <c r="F25">
-        <v>33836.175627161698</v>
-      </c>
-      <c r="G25" s="2"/>
+        <v>33836.1756271617</v>
+      </c>
       <c r="H25">
-        <v>23.299288323865401</v>
+        <v>23.2992883238654</v>
       </c>
       <c r="I25">
-        <v>3.2681336593316401</v>
+        <v>3.26813365933164</v>
       </c>
       <c r="J25">
+        <v>0.951136231422424</v>
+      </c>
+      <c r="K25">
         <v>45.1508795641248</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>240.5</v>
       </c>
-      <c r="L25">
-        <v>-2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>4.8248092625769798</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>4.82480926257698</v>
+      </c>
       <c r="E26">
-        <v>8.3698564385215904E-2</v>
+        <v>0.0836985643852159</v>
       </c>
       <c r="F26">
-        <v>32475.892499219099</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+        <v>32475.8924992191</v>
+      </c>
       <c r="I26">
         <v>2.73853681635243</v>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26">
+      <c r="L26">
         <v>236.1</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>-1.5</v>
       </c>
     </row>

--- a/JPN_WB_timeseries.xlsx
+++ b/JPN_WB_timeseries.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youne\https-github.com-Youncki25-credit-rating-app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1532CF8-B7B2-4A35-A0A9-CB7F725C2F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -61,8 +80,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,13 +144,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -169,7 +196,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -203,6 +230,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -237,9 +265,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,11 +441,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="14" width="66.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -460,7 +492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -468,31 +500,31 @@
         <v>1.22991895675659</v>
       </c>
       <c r="C2">
-        <v>2.63045548903539</v>
+        <v>2.6304554890353899</v>
       </c>
       <c r="D2">
         <v>10.4634942027505</v>
       </c>
       <c r="E2">
-        <v>2.76464755136783</v>
+        <v>2.7646475513678301</v>
       </c>
       <c r="F2">
-        <v>39169.3595701504</v>
+        <v>39169.359570150402</v>
       </c>
       <c r="G2">
         <v>17.1095576406981</v>
       </c>
       <c r="H2">
-        <v>9.09887738115494</v>
+        <v>9.0988773811549404</v>
       </c>
       <c r="I2">
         <v>-0.67657868359508</v>
       </c>
       <c r="J2">
-        <v>1.19755268096924</v>
+        <v>1.1975526809692401</v>
       </c>
       <c r="K2">
-        <v>19.5623715839054</v>
+        <v>19.562371583905399</v>
       </c>
       <c r="L2">
         <v>135.6</v>
@@ -501,33 +533,36 @@
         <v>-7.3</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
+      <c r="B3">
+        <v>1.0123500000000001</v>
+      </c>
       <c r="C3">
         <v>1.97087092323799</v>
       </c>
       <c r="D3">
-        <v>10.0767999632844</v>
+        <v>10.076799963284399</v>
       </c>
       <c r="E3">
-        <v>0.386103426142029</v>
+        <v>0.38610342614202903</v>
       </c>
       <c r="F3">
         <v>34406.1824638092</v>
       </c>
       <c r="G3">
-        <v>16.2333992095233</v>
+        <v>16.233399209523299</v>
       </c>
       <c r="H3">
-        <v>9.48280450872269</v>
+        <v>9.4828045087226904</v>
       </c>
       <c r="I3">
-        <v>-0.740055504162812</v>
+        <v>-0.74005550416281196</v>
       </c>
       <c r="K3">
-        <v>19.5596044720071</v>
+        <v>19.559604472007099</v>
       </c>
       <c r="L3">
         <v>145.1</v>
@@ -536,36 +571,36 @@
         <v>-6.2</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>0.936939835548401</v>
+        <v>0.93693983554840099</v>
       </c>
       <c r="C4">
-        <v>2.60256520794997</v>
+        <v>2.6025652079499699</v>
       </c>
       <c r="D4">
-        <v>10.8554456072287</v>
+        <v>10.855445607228701</v>
       </c>
       <c r="E4">
-        <v>0.0419624992862282</v>
+        <v>4.1962499286228201E-2</v>
       </c>
       <c r="F4">
         <v>32820.7936433254</v>
       </c>
       <c r="G4">
-        <v>16.1070602104528</v>
+        <v>16.107060210452801</v>
       </c>
       <c r="H4">
-        <v>9.5916764589296</v>
+        <v>9.5916764589295997</v>
       </c>
       <c r="I4">
-        <v>-0.923494026942286</v>
+        <v>-0.92349402694228599</v>
       </c>
       <c r="J4">
-        <v>1.17602252960205</v>
+        <v>1.1760225296020499</v>
       </c>
       <c r="K4">
         <v>20.4471220661583</v>
@@ -577,36 +612,36 @@
         <v>-7.3</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>1.16987371444702</v>
+        <v>1.1698737144470199</v>
       </c>
       <c r="C5">
-        <v>3.08393890811207</v>
+        <v>3.0839389081120698</v>
       </c>
       <c r="D5">
         <v>11.4658015766594</v>
       </c>
       <c r="E5">
-        <v>1.53512549946694</v>
+        <v>1.5351254994669401</v>
       </c>
       <c r="F5">
-        <v>35387.0374203599</v>
+        <v>35387.037420359899</v>
       </c>
       <c r="G5">
         <v>15.7293776764486</v>
       </c>
       <c r="H5">
-        <v>9.860323691152489</v>
+        <v>9.8603236911524892</v>
       </c>
       <c r="I5">
-        <v>-0.25654181631606</v>
+        <v>-0.25654181631605999</v>
       </c>
       <c r="J5">
-        <v>1.0271201133728</v>
+        <v>1.0271201133728001</v>
       </c>
       <c r="K5">
         <v>21.3261252678119</v>
@@ -618,39 +653,39 @@
         <v>-7.4</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>1.20001101493835</v>
+        <v>1.2000110149383501</v>
       </c>
       <c r="C6">
-        <v>3.71938350458584</v>
+        <v>3.7193835045858399</v>
       </c>
       <c r="D6">
-        <v>12.7862646247862</v>
+        <v>12.786264624786201</v>
       </c>
       <c r="E6">
-        <v>2.18611569439318</v>
+        <v>2.1861156943931799</v>
       </c>
       <c r="F6">
-        <v>38298.9801712303</v>
+        <v>38298.980171230301</v>
       </c>
       <c r="G6">
-        <v>15.0737560136373</v>
+        <v>15.073756013637301</v>
       </c>
       <c r="H6">
         <v>10.8780887981112</v>
       </c>
       <c r="I6">
-        <v>-0.008573388203060431</v>
+        <v>-8.5733882030604308E-3</v>
       </c>
       <c r="J6">
         <v>1.02831530570984</v>
       </c>
       <c r="K6">
-        <v>23.6643534228975</v>
+        <v>23.664353422897499</v>
       </c>
       <c r="L6">
         <v>169.5</v>
@@ -659,36 +694,36 @@
         <v>-5.3</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>1.2101241350174</v>
+        <v>1.2101241350173999</v>
       </c>
       <c r="C7">
-        <v>3.52114065640567</v>
+        <v>3.5211406564056702</v>
       </c>
       <c r="D7">
-        <v>13.8158957221159</v>
+        <v>13.815895722115901</v>
       </c>
       <c r="E7">
-        <v>1.80390087215821</v>
+        <v>1.8039008721582099</v>
       </c>
       <c r="F7">
-        <v>37812.8950199948</v>
+        <v>37812.895019994801</v>
       </c>
       <c r="G7">
         <v>15.0518407348066</v>
       </c>
       <c r="H7">
-        <v>12.4140588557406</v>
+        <v>12.414058855740601</v>
       </c>
       <c r="I7">
-        <v>-0.282946068764429</v>
+        <v>-0.28294606876442902</v>
       </c>
       <c r="J7">
-        <v>1.03576946258545</v>
+        <v>1.0357694625854501</v>
       </c>
       <c r="K7">
         <v>26.2299545778565</v>
@@ -697,18 +732,18 @@
         <v>174.6</v>
       </c>
       <c r="M7">
-        <v>-4.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>-4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>1.3208487033844</v>
+        <v>1.3208487033844001</v>
       </c>
       <c r="C8">
-        <v>3.79586172862876</v>
+        <v>3.7958617286287599</v>
       </c>
       <c r="D8">
         <v>15.6573740466117</v>
@@ -720,19 +755,19 @@
         <v>35991.546002862</v>
       </c>
       <c r="G8">
-        <v>14.8453333163917</v>
+        <v>14.845333316391701</v>
       </c>
       <c r="H8">
         <v>14.3590020520575</v>
       </c>
       <c r="I8">
-        <v>0.249355116079105</v>
+        <v>0.24935511607910499</v>
       </c>
       <c r="J8">
         <v>1.13833451271057</v>
       </c>
       <c r="K8">
-        <v>30.0163760986692</v>
+        <v>30.016376098669198</v>
       </c>
       <c r="L8">
         <v>174.1</v>
@@ -741,24 +776,24 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>1.23022782802582</v>
+        <v>1.2302278280258201</v>
       </c>
       <c r="C9">
-        <v>4.62330048259255</v>
+        <v>4.6233004825925503</v>
       </c>
       <c r="D9">
-        <v>17.2891273707229</v>
+        <v>17.289127370722898</v>
       </c>
       <c r="E9">
         <v>1.48396941157472</v>
       </c>
       <c r="F9">
-        <v>35779.0245416427</v>
+        <v>35779.024541642699</v>
       </c>
       <c r="G9">
         <v>14.0037943063894</v>
@@ -767,13 +802,13 @@
         <v>15.5274506811561</v>
       </c>
       <c r="I9">
-        <v>0.0600394544986545</v>
+        <v>6.0039454498654499E-2</v>
       </c>
       <c r="J9">
-        <v>1.01037454605103</v>
+        <v>1.0103745460510301</v>
       </c>
       <c r="K9">
-        <v>32.816578051879</v>
+        <v>32.816578051878999</v>
       </c>
       <c r="L9">
         <v>173</v>
@@ -782,48 +817,48 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>1.32388854026794</v>
+        <v>1.3238885402679399</v>
       </c>
       <c r="C10">
         <v>2.78294234789655</v>
       </c>
       <c r="D10">
-        <v>17.2355433764071</v>
+        <v>17.235543376407101</v>
       </c>
       <c r="E10">
-        <v>-1.22428900061713</v>
+        <v>-1.2242890006171301</v>
       </c>
       <c r="F10">
-        <v>39876.3039685725</v>
+        <v>39876.303968572502</v>
       </c>
       <c r="G10">
         <v>15.2644121011595</v>
       </c>
       <c r="H10">
-        <v>16.8939331648175</v>
+        <v>16.893933164817501</v>
       </c>
       <c r="I10">
-        <v>1.38007886164926</v>
+        <v>1.3800788616492601</v>
       </c>
       <c r="J10">
-        <v>0.894625246524811</v>
+        <v>0.89462524652481101</v>
       </c>
       <c r="K10">
-        <v>34.1294765412245</v>
+        <v>34.129476541224498</v>
       </c>
       <c r="L10">
         <v>180.9</v>
       </c>
       <c r="M10">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>-4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -831,13 +866,13 @@
         <v>1.36922454833984</v>
       </c>
       <c r="C11">
-        <v>2.75409583494435</v>
+        <v>2.7540958349443501</v>
       </c>
       <c r="D11">
         <v>12.41956574798</v>
       </c>
       <c r="E11">
-        <v>-5.69323635892741</v>
+        <v>-5.6932363589274102</v>
       </c>
       <c r="F11">
         <v>41308.9968370512</v>
@@ -849,22 +884,22 @@
         <v>11.9706007858756</v>
       </c>
       <c r="I11">
-        <v>-1.35283672951723</v>
+        <v>-1.3528367295172301</v>
       </c>
       <c r="J11">
         <v>0.976251900196075</v>
       </c>
       <c r="K11">
-        <v>24.3901665338555</v>
+        <v>24.390166533855499</v>
       </c>
       <c r="L11">
         <v>198.8</v>
       </c>
       <c r="M11">
-        <v>-9.699999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>-9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -875,28 +910,28 @@
         <v>3.83547896264376</v>
       </c>
       <c r="D12">
-        <v>14.9185034496428</v>
+        <v>14.918503449642801</v>
       </c>
       <c r="E12">
-        <v>4.09791791943181</v>
+        <v>4.0979179194318096</v>
       </c>
       <c r="F12">
-        <v>44968.1562349739</v>
+        <v>44968.156234973903</v>
       </c>
       <c r="G12">
-        <v>17.2217468141394</v>
+        <v>17.221746814139401</v>
       </c>
       <c r="H12">
         <v>13.5799692441961</v>
       </c>
       <c r="I12">
-        <v>-0.7282432075177659</v>
+        <v>-0.72824320751776594</v>
       </c>
       <c r="J12">
-        <v>0.879353165626526</v>
+        <v>0.87935316562652599</v>
       </c>
       <c r="K12">
-        <v>28.4984726938389</v>
+        <v>28.498472693838899</v>
       </c>
       <c r="L12">
         <v>205.9</v>
@@ -905,39 +940,39 @@
         <v>-9.1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>1.55437541007996</v>
+        <v>1.5543754100799601</v>
       </c>
       <c r="C13">
-        <v>2.07915328846556</v>
+        <v>2.0791532884655601</v>
       </c>
       <c r="D13">
         <v>14.7744622613499</v>
       </c>
       <c r="E13">
-        <v>0.0238095237995424</v>
+        <v>2.38095237995424E-2</v>
       </c>
       <c r="F13">
-        <v>48760.0789494211</v>
+        <v>48760.078949421099</v>
       </c>
       <c r="G13">
         <v>18.5956788727445</v>
       </c>
       <c r="H13">
-        <v>15.4204984672798</v>
+        <v>15.420498467279799</v>
       </c>
       <c r="I13">
-        <v>-0.272455616101245</v>
+        <v>-0.27245561610124502</v>
       </c>
       <c r="J13">
-        <v>0.99509197473526</v>
+        <v>0.99509197473526001</v>
       </c>
       <c r="K13">
-        <v>30.1949607286296</v>
+        <v>30.194960728629599</v>
       </c>
       <c r="L13">
         <v>219.2</v>
@@ -946,15 +981,15 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>1.61894869804382</v>
+        <v>1.6189486980438199</v>
       </c>
       <c r="C14">
-        <v>0.95844261141204</v>
+        <v>0.95844261141204001</v>
       </c>
       <c r="D14">
         <v>14.4147746129824</v>
@@ -963,19 +998,19 @@
         <v>1.37475099905274</v>
       </c>
       <c r="F14">
-        <v>49145.2804308193</v>
+        <v>49145.280430819301</v>
       </c>
       <c r="G14">
         <v>18.1117047475127</v>
       </c>
       <c r="H14">
-        <v>16.0561363041928</v>
+        <v>16.056136304192801</v>
       </c>
       <c r="I14">
-        <v>-0.0440645104432608</v>
+        <v>-4.4064510443260797E-2</v>
       </c>
       <c r="J14">
-        <v>0.948442876338959</v>
+        <v>0.94844287633895896</v>
       </c>
       <c r="K14">
         <v>30.4709109171752</v>
@@ -984,10 +1019,10 @@
         <v>226.1</v>
       </c>
       <c r="M14">
-        <v>-8.199999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>-8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -995,31 +1030,31 @@
         <v>1.6482492685318</v>
       </c>
       <c r="C15">
-        <v>0.8897854158088629</v>
+        <v>0.88978541580886295</v>
       </c>
       <c r="D15">
         <v>15.7841567318773</v>
       </c>
       <c r="E15">
-        <v>2.00510017681211</v>
+        <v>2.0051001768121099</v>
       </c>
       <c r="F15">
-        <v>40898.6478964744</v>
+        <v>40898.647896474402</v>
       </c>
       <c r="G15">
-        <v>18.1406509054638</v>
+        <v>18.140650905463801</v>
       </c>
       <c r="H15">
         <v>18.1946119190738</v>
       </c>
       <c r="I15">
-        <v>0.335037912184772</v>
+        <v>0.33503791218477202</v>
       </c>
       <c r="J15">
         <v>1.01914191246033</v>
       </c>
       <c r="K15">
-        <v>33.9787686509511</v>
+        <v>33.978768650951103</v>
       </c>
       <c r="L15">
         <v>229.5</v>
@@ -1028,7 +1063,7 @@
         <v>-7.6</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -1036,31 +1071,31 @@
         <v>1.69021356105804</v>
       </c>
       <c r="C16">
-        <v>0.742322049627638</v>
+        <v>0.74232204962763804</v>
       </c>
       <c r="D16">
-        <v>17.4186553484795</v>
+        <v>17.418655348479501</v>
       </c>
       <c r="E16">
         <v>0.296205514141889</v>
       </c>
       <c r="F16">
-        <v>38475.3952461838</v>
+        <v>38475.395246183798</v>
       </c>
       <c r="G16">
-        <v>17.5741647729135</v>
+        <v>17.574164772913502</v>
       </c>
       <c r="H16">
-        <v>20.0127792201784</v>
+        <v>20.012779220178398</v>
       </c>
       <c r="I16">
-        <v>2.75922671353253</v>
+        <v>2.7592267135325299</v>
       </c>
       <c r="J16">
         <v>0.96859735250473</v>
       </c>
       <c r="K16">
-        <v>37.4314345686579</v>
+        <v>37.431434568657899</v>
       </c>
       <c r="L16">
         <v>233.3</v>
@@ -1069,15 +1104,15 @@
         <v>-5.6</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>1.52976644039154</v>
+        <v>1.5297664403915401</v>
       </c>
       <c r="C17">
-        <v>3.0702796590698</v>
+        <v>3.0702796590697998</v>
       </c>
       <c r="D17">
         <v>17.4367598376529</v>
@@ -1086,22 +1121,22 @@
         <v>1.56062669680782</v>
       </c>
       <c r="F17">
-        <v>34960.6393843385</v>
+        <v>34960.639384338501</v>
       </c>
       <c r="G17">
-        <v>16.9738508264281</v>
+        <v>16.973850826428102</v>
       </c>
       <c r="H17">
-        <v>17.990648516827</v>
+        <v>17.990648516827001</v>
       </c>
       <c r="I17">
-        <v>0.795279630579784</v>
+        <v>0.79527963057978401</v>
       </c>
       <c r="J17">
         <v>1.05422055721283</v>
       </c>
       <c r="K17">
-        <v>35.4274083544798</v>
+        <v>35.427408354479802</v>
       </c>
       <c r="L17">
         <v>228.3</v>
@@ -1110,7 +1145,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -1118,31 +1153,31 @@
         <v>1.4822438955307</v>
       </c>
       <c r="C18">
-        <v>3.93809128404804</v>
+        <v>3.9380912840480402</v>
       </c>
       <c r="D18">
-        <v>16.0579692360598</v>
+        <v>16.057969236059801</v>
       </c>
       <c r="E18">
-        <v>0.753826745789127</v>
+        <v>0.75382674578912701</v>
       </c>
       <c r="F18">
-        <v>39375.4731620781</v>
+        <v>39375.473162078102</v>
       </c>
       <c r="G18">
-        <v>16.7112446327333</v>
+        <v>16.711244632733301</v>
       </c>
       <c r="H18">
-        <v>15.2522776095286</v>
+        <v>15.252277609528599</v>
       </c>
       <c r="I18">
         <v>-0.127258844489712</v>
       </c>
       <c r="J18">
-        <v>0.968189001083374</v>
+        <v>0.96818900108337402</v>
       </c>
       <c r="K18">
-        <v>31.3102468455884</v>
+        <v>31.310246845588399</v>
       </c>
       <c r="L18">
         <v>232.4</v>
@@ -1151,39 +1186,39 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>1.48122704029083</v>
+        <v>1.4812270402908301</v>
       </c>
       <c r="C19">
-        <v>4.12036966283801</v>
+        <v>4.1203696628380104</v>
       </c>
       <c r="D19">
         <v>17.5914391047836</v>
       </c>
       <c r="E19">
-        <v>1.67533175173359</v>
+        <v>1.6753317517335899</v>
       </c>
       <c r="F19">
-        <v>38834.0529341227</v>
+        <v>38834.052934122701</v>
       </c>
       <c r="G19">
         <v>16.1953485344611</v>
       </c>
       <c r="H19">
-        <v>16.831774467385</v>
+        <v>16.831774467384999</v>
       </c>
       <c r="I19">
         <v>0.484199796126422</v>
       </c>
       <c r="J19">
-        <v>1.10012805461884</v>
+        <v>1.1001280546188399</v>
       </c>
       <c r="K19">
-        <v>34.4232135721686</v>
+        <v>34.423213572168599</v>
       </c>
       <c r="L19">
         <v>231.3</v>
@@ -1192,7 +1227,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -1206,25 +1241,25 @@
         <v>18.3149455985223</v>
       </c>
       <c r="E20">
-        <v>0.643391023533141</v>
+        <v>0.64339102353314104</v>
       </c>
       <c r="F20">
-        <v>39751.1330982711</v>
+        <v>39751.133098271101</v>
       </c>
       <c r="G20">
         <v>16.0713191758764</v>
       </c>
       <c r="H20">
-        <v>18.2949862035848</v>
+        <v>18.294986203584799</v>
       </c>
       <c r="I20">
-        <v>0.989094598021811</v>
+        <v>0.98909459802181099</v>
       </c>
       <c r="J20">
-        <v>1.03756272792816</v>
+        <v>1.0375627279281601</v>
       </c>
       <c r="K20">
-        <v>36.609931802107</v>
+        <v>36.609931802106999</v>
       </c>
       <c r="L20">
         <v>232.4</v>
@@ -1233,39 +1268,39 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>1.4309983253479</v>
+        <v>1.4309983253478999</v>
       </c>
       <c r="C21">
         <v>3.45076611445328</v>
       </c>
       <c r="D21">
-        <v>17.4635264275221</v>
+        <v>17.463526427522101</v>
       </c>
       <c r="E21">
-        <v>-0.402169200894946</v>
+        <v>-0.40216920089494601</v>
       </c>
       <c r="F21">
-        <v>40415.9567649547</v>
+        <v>40415.956764954703</v>
       </c>
       <c r="G21">
-        <v>16.4238978704123</v>
+        <v>16.423897870412301</v>
       </c>
       <c r="H21">
         <v>17.7528916808924</v>
       </c>
       <c r="I21">
-        <v>0.468776159383928</v>
+        <v>0.46877615938392803</v>
       </c>
       <c r="J21">
-        <v>1.01981234550476</v>
+        <v>1.0198123455047601</v>
       </c>
       <c r="K21">
-        <v>35.2164181084145</v>
+        <v>35.216418108414501</v>
       </c>
       <c r="L21">
         <v>236.4</v>
@@ -1274,12 +1309,12 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>1.4637143611908</v>
+        <v>1.4637143611907999</v>
       </c>
       <c r="C22">
         <v>2.96847858242384</v>
@@ -1288,19 +1323,19 @@
         <v>15.5331828643222</v>
       </c>
       <c r="E22">
-        <v>-4.16876457146743</v>
+        <v>-4.1687645714674302</v>
       </c>
       <c r="F22">
-        <v>40028.7341726762</v>
+        <v>40028.734172676202</v>
       </c>
       <c r="G22">
-        <v>23.6059009054084</v>
+        <v>23.605900905408401</v>
       </c>
       <c r="H22">
-        <v>15.8020257724508</v>
+        <v>15.802025772450801</v>
       </c>
       <c r="I22">
-        <v>-0.024995834027682</v>
+        <v>-2.4995834027682001E-2</v>
       </c>
       <c r="J22">
         <v>1.02614521980286</v>
@@ -1309,13 +1344,13 @@
         <v>31.335208636773</v>
       </c>
       <c r="L22">
-        <v>258.4</v>
+        <v>258.39999999999998</v>
       </c>
       <c r="M22">
         <v>-9.1</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -1323,31 +1358,31 @@
         <v>1.53576052188873</v>
       </c>
       <c r="C23">
-        <v>3.89996604353179</v>
+        <v>3.8999660435317902</v>
       </c>
       <c r="D23">
-        <v>18.1091919388618</v>
+        <v>18.109191938861802</v>
       </c>
       <c r="E23">
-        <v>2.69657404187188</v>
+        <v>2.6965740418718802</v>
       </c>
       <c r="F23">
         <v>40094.5599795288</v>
       </c>
       <c r="G23">
-        <v>21.6186499931383</v>
+        <v>21.618649993138298</v>
       </c>
       <c r="H23">
-        <v>18.629254289208</v>
+        <v>18.629254289207999</v>
       </c>
       <c r="I23">
-        <v>-0.23335277939831</v>
+        <v>-0.23335277939831001</v>
       </c>
       <c r="J23">
-        <v>1.0155017375946</v>
+        <v>1.0155017375946001</v>
       </c>
       <c r="K23">
-        <v>36.7384462280698</v>
+        <v>36.738446228069797</v>
       </c>
       <c r="L23">
         <v>253.7</v>
@@ -1356,39 +1391,39 @@
         <v>-6.1</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>1.53992962837219</v>
+        <v>1.5399296283721899</v>
       </c>
       <c r="C24">
-        <v>2.11637961936876</v>
+        <v>2.1163796193687601</v>
       </c>
       <c r="D24">
-        <v>21.5464241239166</v>
+        <v>21.546424123916601</v>
       </c>
       <c r="E24">
-        <v>0.941998775483285</v>
+        <v>0.94199877548328503</v>
       </c>
       <c r="F24">
-        <v>34065.6438962526</v>
+        <v>34065.643896252601</v>
       </c>
       <c r="G24">
-        <v>20.9311943137094</v>
+        <v>20.931194313709401</v>
       </c>
       <c r="H24">
-        <v>25.2665627129772</v>
+        <v>25.266562712977201</v>
       </c>
       <c r="I24">
-        <v>2.49770278172251</v>
+        <v>2.4977027817225101</v>
       </c>
       <c r="J24">
         <v>1.0326372385025</v>
       </c>
       <c r="K24">
-        <v>46.8129868368938</v>
+        <v>46.812986836893799</v>
       </c>
       <c r="L24">
         <v>248.2</v>
@@ -1397,12 +1432,12 @@
         <v>-4.2</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>1.3956606388092</v>
+        <v>1.3956606388092001</v>
       </c>
       <c r="C25">
         <v>3.71672795030717</v>
@@ -1414,16 +1449,19 @@
         <v>1.47503481053384</v>
       </c>
       <c r="F25">
-        <v>33836.1756271617</v>
+        <v>33836.175627161698</v>
+      </c>
+      <c r="G25">
+        <v>18.268754629</v>
       </c>
       <c r="H25">
-        <v>23.2992883238654</v>
+        <v>23.299288323865401</v>
       </c>
       <c r="I25">
-        <v>3.26813365933164</v>
+        <v>3.2681336593316401</v>
       </c>
       <c r="J25">
-        <v>0.951136231422424</v>
+        <v>0.95113623142242398</v>
       </c>
       <c r="K25">
         <v>45.1508795641248</v>
@@ -1432,21 +1470,37 @@
         <v>240.5</v>
       </c>
       <c r="M25">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>-2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
+      <c r="B26">
+        <f>AVERAGEA(B2:B25)</f>
+        <v>1.3881960774898519</v>
+      </c>
       <c r="C26">
-        <v>4.82480926257698</v>
+        <v>4.8248092625769798</v>
+      </c>
+      <c r="D26">
+        <f>AVERAGEA(D2:D25)</f>
+        <v>15.5533706256158</v>
       </c>
       <c r="E26">
-        <v>0.0836985643852159</v>
+        <v>8.3698564385215904E-2</v>
       </c>
       <c r="F26">
-        <v>32475.8924992191</v>
+        <v>32475.892499219099</v>
+      </c>
+      <c r="G26">
+        <f>AVERAGEA(G2:G24)</f>
+        <v>17.208938446211196</v>
+      </c>
+      <c r="H26">
+        <f>AVERAGEA(H2:H25)</f>
+        <v>15.519188379556596</v>
       </c>
       <c r="I26">
         <v>2.73853681635243</v>
